--- a/data/SeguimientoCeldas.xlsx
+++ b/data/SeguimientoCeldas.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\project\dashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Documents\project\ubuntu\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2E2CCF-EB67-4DFF-928B-E53BFC03744B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1CD06E-B146-440C-A11F-8B32C7FDA522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Seguimiento" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$55</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
   <si>
     <t>CellName</t>
   </si>
@@ -43,9 +43,6 @@
     <t>MONTE_OLIVOU19_CARR3</t>
   </si>
   <si>
-    <t>STD_STD_CHOFER_21</t>
-  </si>
-  <si>
     <t>LLANO_CHICOU19_CARR5</t>
   </si>
   <si>
@@ -64,15 +61,6 @@
     <t>NAYONU19_CARR2</t>
   </si>
   <si>
-    <t>MOR_TAISHA_HUAWEI3</t>
-  </si>
-  <si>
-    <t>MOR_TAISHA_HUAWEI2</t>
-  </si>
-  <si>
-    <t>MOR_TAISHA_HUAWEI1</t>
-  </si>
-  <si>
     <t>NAYONU19_CARR4</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>NODO3_GUAJALO_SAN_MARTIN1_CARR1</t>
   </si>
   <si>
-    <t>NODO3_GUAJALO_SAN_MARTIN1_CARR5</t>
-  </si>
-  <si>
     <t>NAYONU19_CARR5</t>
   </si>
   <si>
@@ -115,42 +100,15 @@
     <t>ESM_ATA_ATACAMES_SUR_U19_1</t>
   </si>
   <si>
-    <t>PIC_UIO_MAQUETA_VSAT_EST_TERRENA_U19_2</t>
-  </si>
-  <si>
-    <t>STD_STD_CIUDAD_VERDE_U19_2</t>
-  </si>
-  <si>
-    <t>PIC_UIO_MAQUETA_VSAT_EST_TERRENA_U19_1</t>
-  </si>
-  <si>
     <t>Seguimiento</t>
   </si>
   <si>
-    <t>Celda Bloqueada</t>
-  </si>
-  <si>
-    <t>Sitio Apagado</t>
-  </si>
-  <si>
     <t>Sitio Caido</t>
   </si>
   <si>
     <t>Celda Carretera</t>
   </si>
   <si>
-    <t>STD_STD_CHOFER_2_APT_7</t>
-  </si>
-  <si>
-    <t>43663-7</t>
-  </si>
-  <si>
-    <t>Celda Bloqueada (Cárcel Sto Domingo)</t>
-  </si>
-  <si>
-    <t>NAYONU19_CARR6</t>
-  </si>
-  <si>
     <t>COL_ALEMAN_TRR3</t>
   </si>
   <si>
@@ -163,30 +121,12 @@
     <t>MONTE_OLIVOU19_CARR2</t>
   </si>
   <si>
-    <t>SMALL_UIO_REPUBLICA1</t>
-  </si>
-  <si>
     <t>AUTOPISTAU19_CARR3</t>
   </si>
   <si>
     <t>NODO3_GUAJALO_SAN_MARTIN2_CARR1</t>
   </si>
   <si>
-    <t>NODO3_GUAJALO_SAN_MARTIN2_CARR6</t>
-  </si>
-  <si>
-    <t>NODO3_GUAJALO_SAN_MARTIN2_CARR5</t>
-  </si>
-  <si>
-    <t>NODO3_GUAJALO_SAN_MARTIN1_CARR6</t>
-  </si>
-  <si>
-    <t>RESERVORIO_PUENGASI4</t>
-  </si>
-  <si>
-    <t>SUC_SHU_SHUSHUFINDI_OESTE_U19_2</t>
-  </si>
-  <si>
     <t>PI_UIO_COL_EINSTEIN_1</t>
   </si>
   <si>
@@ -196,13 +136,97 @@
     <t>Sitio Desmontado</t>
   </si>
   <si>
-    <t>Pendiente Revisar Fibra</t>
-  </si>
-  <si>
     <t>Problemas de Acceso</t>
   </si>
   <si>
-    <t>Small Desmontada</t>
+    <t>COW_INTER_CUMBAYAU19_CARRU4</t>
+  </si>
+  <si>
+    <t>COW_INTER_CUMBAYAU19_CARRU1</t>
+  </si>
+  <si>
+    <t>TONSUPA3</t>
+  </si>
+  <si>
+    <t>TONSUPA2</t>
+  </si>
+  <si>
+    <t>TONSUPA1</t>
+  </si>
+  <si>
+    <t>TONSUPA9</t>
+  </si>
+  <si>
+    <t>TONSUPA8</t>
+  </si>
+  <si>
+    <t>ES_ATA_TONSUPA_1</t>
+  </si>
+  <si>
+    <t>44603-1</t>
+  </si>
+  <si>
+    <t>ES_ATA_TONSUPA_2</t>
+  </si>
+  <si>
+    <t>44603-2</t>
+  </si>
+  <si>
+    <t>ES_ATA_TONSUPA_3</t>
+  </si>
+  <si>
+    <t>44603-3</t>
+  </si>
+  <si>
+    <t>LLANO_CHICOU19_CARR3</t>
+  </si>
+  <si>
+    <t>LLANO_CHICOU19_CARR2</t>
+  </si>
+  <si>
+    <t>LLANO_CHICOU19_CARR1</t>
+  </si>
+  <si>
+    <t>MONTE_OLIVOU19_CARR6</t>
+  </si>
+  <si>
+    <t>MONTE_OLIVOU19_CARR5</t>
+  </si>
+  <si>
+    <t>NAYONU19_CARR3</t>
+  </si>
+  <si>
+    <t>NODO3_GUAJALO_SAN_MARTIN1_CARR4</t>
+  </si>
+  <si>
+    <t>REAL_AUDIENCIA1</t>
+  </si>
+  <si>
+    <t>PIC_SMALL_ANT1</t>
+  </si>
+  <si>
+    <t>PIC_UIO_ODEBRECHT_U19_3</t>
+  </si>
+  <si>
+    <t>PIC_UIO_ODEBRECHT_U19_2</t>
+  </si>
+  <si>
+    <t>PIC_UIO_ODEBRECHT_U19_1</t>
+  </si>
+  <si>
+    <t>SD_SD_LIBERTADOR_1</t>
+  </si>
+  <si>
+    <t>44767-1</t>
+  </si>
+  <si>
+    <t>SMALL_UIO_MARRIOT1</t>
+  </si>
+  <si>
+    <t>Pendiente Cambio RRU</t>
+  </si>
+  <si>
+    <t>Pendiente Trabajos Infraestructura</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BDB550-E1E7-404D-B978-F462E546FC21}">
-  <dimension ref="A1:D3736"/>
+  <dimension ref="A1:D3689"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
@@ -1059,59 +1083,59 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>36631</v>
+        <v>49501</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>38032</v>
+        <v>49503</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>46421</v>
+        <v>49504</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>49505</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
-      </c>
-      <c r="B5">
-        <v>46422</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6">
-        <v>46423</v>
+        <v>49641</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -1119,384 +1143,384 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>48741</v>
+        <v>49642</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>48742</v>
+        <v>49643</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B9">
-        <v>48743</v>
+        <v>49511</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>49501</v>
+        <v>49512</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B11">
-        <v>49504</v>
+        <v>49514</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>49505</v>
+        <v>49515</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13">
-        <v>49512</v>
+        <v>49516</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>49515</v>
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>49516</v>
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>49524</v>
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>49525</v>
+        <v>46421</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B18">
-        <v>49531</v>
+        <v>46422</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>49533</v>
+        <v>46423</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B20">
-        <v>49534</v>
+        <v>49521</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B21">
-        <v>49537</v>
+        <v>49522</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B22">
-        <v>49542</v>
+        <v>49523</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B23">
-        <v>49544</v>
+        <v>49524</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>49545</v>
+        <v>49525</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B25">
-        <v>49551</v>
+        <v>49531</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B26">
-        <v>49555</v>
+        <v>49532</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B27">
-        <v>49562</v>
+        <v>49533</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B28">
-        <v>49563</v>
+        <v>49534</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B29">
-        <v>49574</v>
+        <v>49535</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B30">
-        <v>49575</v>
+        <v>49536</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B31">
-        <v>49761</v>
+        <v>49537</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B32">
-        <v>49762</v>
+        <v>49542</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
+        <v>56</v>
+      </c>
+      <c r="B33">
+        <v>49543</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B34">
-        <v>49546</v>
+        <v>49544</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B35">
-        <v>49643</v>
+        <v>49545</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>49642</v>
+        <v>49551</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B37">
-        <v>49641</v>
+        <v>49554</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B38">
-        <v>49532</v>
+        <v>49561</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B39">
-        <v>32151</v>
+        <v>49562</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B40">
-        <v>49503</v>
+        <v>49563</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41">
-        <v>49561</v>
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
       </c>
       <c r="C41" t="s">
         <v>37</v>
@@ -1504,117 +1528,347 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B42">
-        <v>49566</v>
+        <v>32801</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B43">
-        <v>49565</v>
+        <v>42481</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B44">
-        <v>49556</v>
+        <v>42482</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B45">
-        <v>43454</v>
+        <v>42483</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B46">
-        <v>33222</v>
+        <v>41481</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="1049" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1049" s="1"/>
-    </row>
-    <row r="1188" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1188" s="1"/>
-    </row>
-    <row r="1380" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1380" s="1"/>
-    </row>
-    <row r="1564" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1564" s="1"/>
-    </row>
-    <row r="1618" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1618" s="1"/>
-    </row>
-    <row r="1696" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1696" s="1"/>
-    </row>
-    <row r="2102" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2102" s="1"/>
-    </row>
-    <row r="2184" spans="3:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48">
+        <v>32061</v>
+      </c>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49">
+        <v>49574</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50">
+        <v>49575</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51">
+        <v>46031</v>
+      </c>
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52">
+        <v>46032</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53">
+        <v>46033</v>
+      </c>
+      <c r="C53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54">
+        <v>46038</v>
+      </c>
+      <c r="C54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55">
+        <v>46039</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1002" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1002" s="1"/>
+    </row>
+    <row r="1141" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1141" s="1"/>
+    </row>
+    <row r="1333" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1333" s="1"/>
+    </row>
+    <row r="1517" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1517" s="1"/>
+    </row>
+    <row r="1571" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1571" s="1"/>
+    </row>
+    <row r="1649" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1649" s="1"/>
+    </row>
+    <row r="2055" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D2055" s="1"/>
+    </row>
+    <row r="2137" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2137" s="1"/>
+    </row>
+    <row r="2138" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2138" s="1"/>
+    </row>
+    <row r="2139" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2139" s="1"/>
+    </row>
+    <row r="2140" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2140" s="1"/>
+    </row>
+    <row r="2141" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2141" s="1"/>
+    </row>
+    <row r="2142" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2142" s="1"/>
+    </row>
+    <row r="2143" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2143" s="1"/>
+    </row>
+    <row r="2144" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2144" s="1"/>
+    </row>
+    <row r="2145" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2145" s="1"/>
+    </row>
+    <row r="2146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2146" s="1"/>
+    </row>
+    <row r="2147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2147" s="1"/>
+    </row>
+    <row r="2148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2148" s="1"/>
+    </row>
+    <row r="2149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2149" s="1"/>
+    </row>
+    <row r="2150" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2150" s="1"/>
+    </row>
+    <row r="2151" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2151" s="1"/>
+    </row>
+    <row r="2152" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2152" s="1"/>
+    </row>
+    <row r="2153" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2153" s="1"/>
+    </row>
+    <row r="2154" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2154" s="1"/>
+    </row>
+    <row r="2155" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2155" s="1"/>
+    </row>
+    <row r="2156" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2156" s="1"/>
+    </row>
+    <row r="2157" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2157" s="1"/>
+    </row>
+    <row r="2158" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2158" s="1"/>
+    </row>
+    <row r="2159" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2159" s="1"/>
+    </row>
+    <row r="2160" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2160" s="1"/>
+    </row>
+    <row r="2161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2161" s="1"/>
+    </row>
+    <row r="2162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2162" s="1"/>
+    </row>
+    <row r="2163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2163" s="1"/>
+    </row>
+    <row r="2164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2164" s="1"/>
+    </row>
+    <row r="2165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2165" s="1"/>
+    </row>
+    <row r="2166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2166" s="1"/>
+    </row>
+    <row r="2167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2167" s="1"/>
+    </row>
+    <row r="2168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2168" s="1"/>
+    </row>
+    <row r="2169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2169" s="1"/>
+    </row>
+    <row r="2170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2170" s="1"/>
+    </row>
+    <row r="2171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2171" s="1"/>
+    </row>
+    <row r="2172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2172" s="1"/>
+    </row>
+    <row r="2173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2173" s="1"/>
+    </row>
+    <row r="2174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2174" s="1"/>
+    </row>
+    <row r="2175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2175" s="1"/>
+    </row>
+    <row r="2176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2176" s="1"/>
+    </row>
+    <row r="2177" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2177" s="1"/>
+    </row>
+    <row r="2178" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2178" s="1"/>
+    </row>
+    <row r="2179" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2179" s="1"/>
+    </row>
+    <row r="2180" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2180" s="1"/>
+    </row>
+    <row r="2181" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2181" s="1"/>
+    </row>
+    <row r="2182" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2182" s="1"/>
+    </row>
+    <row r="2183" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C2183" s="1"/>
+    </row>
+    <row r="2184" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2184" s="1"/>
     </row>
-    <row r="2185" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2185" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2185" s="1"/>
     </row>
-    <row r="2186" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2186" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2186" s="1"/>
     </row>
-    <row r="2187" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2187" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2187" s="1"/>
     </row>
-    <row r="2188" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2188" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2188" s="1"/>
     </row>
-    <row r="2189" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2189" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2189" s="1"/>
     </row>
-    <row r="2190" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2190" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2190" s="1"/>
     </row>
-    <row r="2191" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2191" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2191" s="1"/>
     </row>
-    <row r="2192" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2192" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2192" s="1"/>
+      <c r="D2192" s="1"/>
     </row>
     <row r="2193" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2193" s="1"/>
@@ -1709,56 +1963,52 @@
     <row r="2223" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2223" s="1"/>
     </row>
-    <row r="2224" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2224" s="1"/>
-    </row>
-    <row r="2225" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2225" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2225" s="1"/>
     </row>
-    <row r="2226" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2226" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2226" s="1"/>
     </row>
-    <row r="2227" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2227" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2227" s="1"/>
     </row>
-    <row r="2228" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2228" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2228" s="1"/>
     </row>
-    <row r="2229" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2229" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2229" s="1"/>
     </row>
-    <row r="2230" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2230" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2230" s="1"/>
     </row>
-    <row r="2231" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2231" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2231" s="1"/>
     </row>
-    <row r="2232" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2232" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2232" s="1"/>
     </row>
-    <row r="2233" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2233" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2233" s="1"/>
     </row>
-    <row r="2234" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2234" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2234" s="1"/>
     </row>
-    <row r="2235" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2235" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2235" s="1"/>
     </row>
-    <row r="2236" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2236" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2236" s="1"/>
     </row>
-    <row r="2237" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2237" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2237" s="1"/>
     </row>
-    <row r="2238" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2238" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2238" s="1"/>
     </row>
-    <row r="2239" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2239" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2239" s="1"/>
-      <c r="D2239" s="1"/>
-    </row>
-    <row r="2240" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2240" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2240" s="1"/>
     </row>
     <row r="2241" spans="3:3" x14ac:dyDescent="0.25">
@@ -1851,6 +2101,9 @@
     <row r="2270" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2270" s="1"/>
     </row>
+    <row r="2271" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2271" s="1"/>
+    </row>
     <row r="2272" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2272" s="1"/>
     </row>
@@ -2094,101 +2347,103 @@
     <row r="2352" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2352" s="1"/>
     </row>
-    <row r="2353" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2353" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2353" s="1"/>
     </row>
-    <row r="2354" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2354" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2354" s="1"/>
     </row>
-    <row r="2355" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2355" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2355" s="1"/>
     </row>
-    <row r="2356" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2356" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2356" s="1"/>
     </row>
-    <row r="2357" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2357" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2357" s="1"/>
     </row>
-    <row r="2358" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2358" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2358" s="1"/>
     </row>
-    <row r="2359" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2359" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2359" s="1"/>
     </row>
-    <row r="2360" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2360" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2360" s="1"/>
     </row>
-    <row r="2361" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2361" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2361" s="1"/>
-    </row>
-    <row r="2362" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2361" s="1"/>
+    </row>
+    <row r="2362" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2362" s="1"/>
     </row>
-    <row r="2363" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2363" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2363" s="1"/>
     </row>
-    <row r="2364" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2364" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2364" s="1"/>
     </row>
-    <row r="2365" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2365" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2365" s="1"/>
     </row>
-    <row r="2366" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2366" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2366" s="1"/>
     </row>
-    <row r="2367" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2367" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2367" s="1"/>
     </row>
-    <row r="2368" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2368" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2368" s="1"/>
     </row>
-    <row r="2369" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2369" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2369" s="1"/>
     </row>
-    <row r="2370" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2370" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2370" s="1"/>
     </row>
-    <row r="2371" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2371" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2371" s="1"/>
     </row>
-    <row r="2372" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2372" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2372" s="1"/>
     </row>
-    <row r="2373" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2373" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2373" s="1"/>
     </row>
-    <row r="2374" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2374" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2374" s="1"/>
     </row>
-    <row r="2375" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2375" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2375" s="1"/>
     </row>
-    <row r="2376" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2376" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2376" s="1"/>
     </row>
-    <row r="2377" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2377" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2377" s="1"/>
     </row>
-    <row r="2378" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2378" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2378" s="1"/>
     </row>
-    <row r="2379" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2379" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2379" s="1"/>
     </row>
-    <row r="2380" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2380" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2380" s="1"/>
     </row>
-    <row r="2381" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2381" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2381" s="1"/>
     </row>
-    <row r="2382" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2382" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2382" s="1"/>
     </row>
-    <row r="2383" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2383" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2383" s="1"/>
     </row>
-    <row r="2384" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2384" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2384" s="1"/>
+      <c r="D2384" s="1"/>
     </row>
     <row r="2385" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2385" s="1"/>
@@ -2238,102 +2493,100 @@
     <row r="2400" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2400" s="1"/>
     </row>
-    <row r="2401" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2401" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2401" s="1"/>
     </row>
-    <row r="2402" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2402" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2402" s="1"/>
     </row>
-    <row r="2403" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2403" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2403" s="1"/>
     </row>
-    <row r="2404" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2404" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2404" s="1"/>
     </row>
-    <row r="2405" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2405" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2405" s="1"/>
     </row>
-    <row r="2406" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2406" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2406" s="1"/>
     </row>
-    <row r="2407" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2407" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2407" s="1"/>
     </row>
-    <row r="2408" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2408" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2408" s="1"/>
-      <c r="D2408" s="1"/>
-    </row>
-    <row r="2409" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2409" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2409" s="1"/>
     </row>
-    <row r="2410" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2410" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2410" s="1"/>
     </row>
-    <row r="2411" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2411" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2411" s="1"/>
     </row>
-    <row r="2412" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2412" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2412" s="1"/>
     </row>
-    <row r="2413" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2413" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2413" s="1"/>
     </row>
-    <row r="2414" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2414" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2414" s="1"/>
     </row>
-    <row r="2415" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2415" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2415" s="1"/>
     </row>
-    <row r="2416" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2416" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2416" s="1"/>
     </row>
-    <row r="2417" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2417" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2417" s="1"/>
     </row>
-    <row r="2418" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2418" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2418" s="1"/>
     </row>
-    <row r="2419" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2419" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2419" s="1"/>
     </row>
-    <row r="2420" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2420" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2420" s="1"/>
     </row>
-    <row r="2421" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2421" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2421" s="1"/>
     </row>
-    <row r="2422" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2422" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2422" s="1"/>
     </row>
-    <row r="2423" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2423" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2423" s="1"/>
     </row>
-    <row r="2424" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2424" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2424" s="1"/>
     </row>
-    <row r="2425" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2425" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2425" s="1"/>
     </row>
-    <row r="2426" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2426" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2426" s="1"/>
     </row>
-    <row r="2427" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2427" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2427" s="1"/>
     </row>
-    <row r="2428" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2428" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2428" s="1"/>
     </row>
-    <row r="2429" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2429" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2429" s="1"/>
     </row>
-    <row r="2430" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2430" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2430" s="1"/>
     </row>
-    <row r="2431" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2431" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2431" s="1"/>
-      <c r="D2431" s="1"/>
-    </row>
-    <row r="2432" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2432" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2432" s="1"/>
     </row>
     <row r="2433" spans="3:3" x14ac:dyDescent="0.25">
@@ -2768,52 +3021,53 @@
     <row r="2576" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2576" s="1"/>
     </row>
-    <row r="2577" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2577" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2577" s="1"/>
     </row>
-    <row r="2578" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2578" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2578" s="1"/>
     </row>
-    <row r="2579" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2579" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2579" s="1"/>
     </row>
-    <row r="2580" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2580" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2580" s="1"/>
     </row>
-    <row r="2581" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2581" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2581" s="1"/>
     </row>
-    <row r="2582" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2582" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2582" s="1"/>
     </row>
-    <row r="2583" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2583" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2583" s="1"/>
     </row>
-    <row r="2584" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2584" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2584" s="1"/>
     </row>
-    <row r="2585" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2585" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2585" s="1"/>
     </row>
-    <row r="2586" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2586" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2586" s="1"/>
     </row>
-    <row r="2587" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2587" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2587" s="1"/>
-    </row>
-    <row r="2588" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2587" s="1"/>
+    </row>
+    <row r="2588" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2588" s="1"/>
     </row>
-    <row r="2589" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2589" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2589" s="1"/>
     </row>
-    <row r="2590" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2590" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2590" s="1"/>
     </row>
-    <row r="2591" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2591" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2591" s="1"/>
     </row>
-    <row r="2592" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2592" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2592" s="1"/>
     </row>
     <row r="2593" spans="3:3" x14ac:dyDescent="0.25">
@@ -2864,101 +3118,101 @@
     <row r="2608" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2608" s="1"/>
     </row>
-    <row r="2609" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2609" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2609" s="1"/>
     </row>
-    <row r="2610" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2610" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2610" s="1"/>
     </row>
-    <row r="2611" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2611" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2611" s="1"/>
     </row>
-    <row r="2612" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2612" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2612" s="1"/>
     </row>
-    <row r="2613" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2613" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2613" s="1"/>
     </row>
-    <row r="2614" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2614" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2614" s="1"/>
     </row>
-    <row r="2615" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2615" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2615" s="1"/>
     </row>
-    <row r="2616" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2616" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2616" s="1"/>
     </row>
-    <row r="2617" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2617" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2617" s="1"/>
     </row>
-    <row r="2618" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2618" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2618" s="1"/>
-    </row>
-    <row r="2619" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2618" s="1"/>
+    </row>
+    <row r="2619" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2619" s="1"/>
     </row>
-    <row r="2620" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2620" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2620" s="1"/>
     </row>
-    <row r="2621" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2621" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2621" s="1"/>
     </row>
-    <row r="2622" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2622" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2622" s="1"/>
     </row>
-    <row r="2623" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2623" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2623" s="1"/>
     </row>
-    <row r="2624" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2624" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2624" s="1"/>
     </row>
-    <row r="2625" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2625" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2625" s="1"/>
     </row>
-    <row r="2626" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2626" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2626" s="1"/>
     </row>
-    <row r="2627" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2627" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2627" s="1"/>
     </row>
-    <row r="2628" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2628" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2628" s="1"/>
     </row>
-    <row r="2629" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2629" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2629" s="1"/>
     </row>
-    <row r="2630" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2630" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2630" s="1"/>
     </row>
-    <row r="2631" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2631" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2631" s="1"/>
     </row>
-    <row r="2632" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2632" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2632" s="1"/>
     </row>
-    <row r="2633" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2633" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2633" s="1"/>
     </row>
-    <row r="2634" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2634" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2634" s="1"/>
-      <c r="D2634" s="1"/>
-    </row>
-    <row r="2635" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2635" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2635" s="1"/>
     </row>
-    <row r="2636" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2636" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2636" s="1"/>
     </row>
-    <row r="2637" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2637" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2637" s="1"/>
     </row>
-    <row r="2638" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2638" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2638" s="1"/>
     </row>
-    <row r="2639" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2639" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2639" s="1"/>
     </row>
-    <row r="2640" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2640" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2640" s="1"/>
     </row>
     <row r="2641" spans="3:3" x14ac:dyDescent="0.25">
@@ -3009,53 +3263,52 @@
     <row r="2656" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2656" s="1"/>
     </row>
-    <row r="2657" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2657" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2657" s="1"/>
     </row>
-    <row r="2658" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2658" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2658" s="1"/>
     </row>
-    <row r="2659" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2659" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2659" s="1"/>
     </row>
-    <row r="2660" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2660" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2660" s="1"/>
     </row>
-    <row r="2661" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2661" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2661" s="1"/>
     </row>
-    <row r="2662" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2662" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2662" s="1"/>
     </row>
-    <row r="2663" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2663" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2663" s="1"/>
     </row>
-    <row r="2664" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2664" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2664" s="1"/>
     </row>
-    <row r="2665" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2665" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2665" s="1"/>
-      <c r="D2665" s="1"/>
-    </row>
-    <row r="2666" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2666" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2666" s="1"/>
     </row>
-    <row r="2667" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2667" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2667" s="1"/>
     </row>
-    <row r="2668" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2668" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2668" s="1"/>
     </row>
-    <row r="2669" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2669" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2669" s="1"/>
     </row>
-    <row r="2670" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2670" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2670" s="1"/>
     </row>
-    <row r="2671" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2671" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2671" s="1"/>
     </row>
-    <row r="2672" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2672" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2672" s="1"/>
     </row>
     <row r="2673" spans="3:3" x14ac:dyDescent="0.25">
@@ -3298,52 +3551,53 @@
     <row r="2752" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2752" s="1"/>
     </row>
-    <row r="2753" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2753" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2753" s="1"/>
     </row>
-    <row r="2754" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2754" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2754" s="1"/>
     </row>
-    <row r="2755" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2755" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2755" s="1"/>
     </row>
-    <row r="2756" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2756" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2756" s="1"/>
     </row>
-    <row r="2757" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2757" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2757" s="1"/>
     </row>
-    <row r="2758" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2758" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2758" s="1"/>
     </row>
-    <row r="2759" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2759" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2759" s="1"/>
     </row>
-    <row r="2760" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2760" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2760" s="1"/>
     </row>
-    <row r="2761" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2761" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2761" s="1"/>
     </row>
-    <row r="2762" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2762" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2762" s="1"/>
     </row>
-    <row r="2763" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2763" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2763" s="1"/>
-    </row>
-    <row r="2764" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2763" s="1"/>
+    </row>
+    <row r="2764" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2764" s="1"/>
     </row>
-    <row r="2765" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2765" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2765" s="1"/>
     </row>
-    <row r="2766" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2766" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2766" s="1"/>
     </row>
-    <row r="2767" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2767" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2767" s="1"/>
     </row>
-    <row r="2768" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2768" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2768" s="1"/>
     </row>
     <row r="2769" spans="3:3" x14ac:dyDescent="0.25">
@@ -3442,53 +3696,52 @@
     <row r="2800" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2800" s="1"/>
     </row>
-    <row r="2801" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2801" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2801" s="1"/>
     </row>
-    <row r="2802" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2802" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2802" s="1"/>
     </row>
-    <row r="2803" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2803" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2803" s="1"/>
     </row>
-    <row r="2804" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2804" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2804" s="1"/>
     </row>
-    <row r="2805" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2805" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2805" s="1"/>
     </row>
-    <row r="2806" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2806" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2806" s="1"/>
     </row>
-    <row r="2807" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2807" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2807" s="1"/>
     </row>
-    <row r="2808" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2808" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2808" s="1"/>
     </row>
-    <row r="2809" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2809" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2809" s="1"/>
     </row>
-    <row r="2810" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2810" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2810" s="1"/>
-      <c r="D2810" s="1"/>
-    </row>
-    <row r="2811" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2811" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2811" s="1"/>
     </row>
-    <row r="2812" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2812" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2812" s="1"/>
     </row>
-    <row r="2813" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2813" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2813" s="1"/>
     </row>
-    <row r="2814" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2814" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2814" s="1"/>
     </row>
-    <row r="2815" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2815" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2815" s="1"/>
     </row>
-    <row r="2816" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2816" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2816" s="1"/>
     </row>
     <row r="2817" spans="3:3" x14ac:dyDescent="0.25">
@@ -3539,52 +3792,53 @@
     <row r="2832" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2832" s="1"/>
     </row>
-    <row r="2833" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2833" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2833" s="1"/>
     </row>
-    <row r="2834" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2834" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2834" s="1"/>
     </row>
-    <row r="2835" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2835" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2835" s="1"/>
     </row>
-    <row r="2836" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2836" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2836" s="1"/>
     </row>
-    <row r="2837" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2837" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2837" s="1"/>
     </row>
-    <row r="2838" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2838" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2838" s="1"/>
     </row>
-    <row r="2839" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2839" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2839" s="1"/>
     </row>
-    <row r="2840" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2840" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2840" s="1"/>
     </row>
-    <row r="2841" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2841" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2841" s="1"/>
     </row>
-    <row r="2842" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2842" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2842" s="1"/>
     </row>
-    <row r="2843" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2843" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2843" s="1"/>
-    </row>
-    <row r="2844" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2843" s="1"/>
+    </row>
+    <row r="2844" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2844" s="1"/>
     </row>
-    <row r="2845" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2845" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2845" s="1"/>
     </row>
-    <row r="2846" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2846" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2846" s="1"/>
     </row>
-    <row r="2847" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2847" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2847" s="1"/>
     </row>
-    <row r="2848" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2848" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2848" s="1"/>
     </row>
     <row r="2849" spans="3:3" x14ac:dyDescent="0.25">
@@ -3635,101 +3889,101 @@
     <row r="2864" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2864" s="1"/>
     </row>
-    <row r="2865" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2865" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2865" s="1"/>
     </row>
-    <row r="2866" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2866" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2866" s="1"/>
     </row>
-    <row r="2867" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2867" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2867" s="1"/>
     </row>
-    <row r="2868" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2868" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2868" s="1"/>
     </row>
-    <row r="2869" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2869" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2869" s="1"/>
     </row>
-    <row r="2870" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2870" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2870" s="1"/>
     </row>
-    <row r="2871" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2871" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2871" s="1"/>
     </row>
-    <row r="2872" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2872" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2872" s="1"/>
     </row>
-    <row r="2873" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2873" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2873" s="1"/>
     </row>
-    <row r="2874" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2874" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2874" s="1"/>
     </row>
-    <row r="2875" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2875" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2875" s="1"/>
     </row>
-    <row r="2876" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2876" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2876" s="1"/>
     </row>
-    <row r="2877" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2877" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2877" s="1"/>
     </row>
-    <row r="2878" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2878" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2878" s="1"/>
-    </row>
-    <row r="2879" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2878" s="1"/>
+    </row>
+    <row r="2879" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2879" s="1"/>
     </row>
-    <row r="2880" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2880" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2880" s="1"/>
     </row>
-    <row r="2881" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2881" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2881" s="1"/>
     </row>
-    <row r="2882" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2882" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2882" s="1"/>
     </row>
-    <row r="2883" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2883" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2883" s="1"/>
     </row>
-    <row r="2884" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2884" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2884" s="1"/>
     </row>
-    <row r="2885" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2885" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2885" s="1"/>
     </row>
-    <row r="2886" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2886" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2886" s="1"/>
     </row>
-    <row r="2887" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2887" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2887" s="1"/>
     </row>
-    <row r="2888" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2888" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2888" s="1"/>
     </row>
-    <row r="2889" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2889" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2889" s="1"/>
     </row>
-    <row r="2890" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2890" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2890" s="1"/>
-      <c r="D2890" s="1"/>
-    </row>
-    <row r="2891" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2891" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2891" s="1"/>
     </row>
-    <row r="2892" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2892" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2892" s="1"/>
     </row>
-    <row r="2893" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2893" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2893" s="1"/>
     </row>
-    <row r="2894" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2894" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2894" s="1"/>
     </row>
-    <row r="2895" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2895" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2895" s="1"/>
     </row>
-    <row r="2896" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2896" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2896" s="1"/>
     </row>
     <row r="2897" spans="3:3" x14ac:dyDescent="0.25">
@@ -3780,102 +4034,102 @@
     <row r="2912" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2912" s="1"/>
     </row>
-    <row r="2913" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2913" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2913" s="1"/>
     </row>
-    <row r="2914" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2914" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2914" s="1"/>
     </row>
-    <row r="2915" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2915" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2915" s="1"/>
     </row>
-    <row r="2916" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2916" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2916" s="1"/>
     </row>
-    <row r="2917" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2917" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2917" s="1"/>
     </row>
-    <row r="2918" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2918" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2918" s="1"/>
     </row>
-    <row r="2919" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2919" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2919" s="1"/>
     </row>
-    <row r="2920" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2920" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2920" s="1"/>
     </row>
-    <row r="2921" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2921" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2921" s="1"/>
     </row>
-    <row r="2922" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2922" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2922" s="1"/>
     </row>
-    <row r="2923" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2923" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2923" s="1"/>
     </row>
-    <row r="2924" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2924" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2924" s="1"/>
     </row>
-    <row r="2925" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2925" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2925" s="1"/>
-      <c r="D2925" s="1"/>
-    </row>
-    <row r="2926" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2926" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2926" s="1"/>
     </row>
-    <row r="2927" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2927" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2927" s="1"/>
     </row>
-    <row r="2928" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2928" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2928" s="1"/>
     </row>
-    <row r="2929" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2929" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2929" s="1"/>
     </row>
-    <row r="2930" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2930" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2930" s="1"/>
     </row>
-    <row r="2931" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2931" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2931" s="1"/>
     </row>
-    <row r="2932" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2932" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2932" s="1"/>
     </row>
-    <row r="2933" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2933" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2933" s="1"/>
     </row>
-    <row r="2934" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2934" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2934" s="1"/>
     </row>
-    <row r="2935" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2935" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2935" s="1"/>
     </row>
-    <row r="2936" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2936" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2936" s="1"/>
     </row>
-    <row r="2937" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2937" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2937" s="1"/>
     </row>
-    <row r="2938" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2938" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2938" s="1"/>
     </row>
-    <row r="2939" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2939" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2939" s="1"/>
     </row>
-    <row r="2940" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2940" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2940" s="1"/>
     </row>
-    <row r="2941" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2941" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2941" s="1"/>
     </row>
-    <row r="2942" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2942" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2942" s="1"/>
     </row>
-    <row r="2943" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2943" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2943" s="1"/>
     </row>
-    <row r="2944" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2944" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2944" s="1"/>
+      <c r="D2944" s="1"/>
     </row>
     <row r="2945" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2945" s="1"/>
@@ -3987,6 +4241,7 @@
     </row>
     <row r="2981" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2981" s="1"/>
+      <c r="D2981" s="1"/>
     </row>
     <row r="2982" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2982" s="1"/>
@@ -4017,7 +4272,6 @@
     </row>
     <row r="2991" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2991" s="1"/>
-      <c r="D2991" s="1"/>
     </row>
     <row r="2992" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2992" s="1"/>
@@ -4118,53 +4372,52 @@
     <row r="3024" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3024" s="1"/>
     </row>
-    <row r="3025" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3025" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3025" s="1"/>
     </row>
-    <row r="3026" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3026" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3026" s="1"/>
     </row>
-    <row r="3027" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3027" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3027" s="1"/>
     </row>
-    <row r="3028" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3028" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3028" s="1"/>
-      <c r="D3028" s="1"/>
-    </row>
-    <row r="3029" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3029" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3029" s="1"/>
     </row>
-    <row r="3030" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3030" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3030" s="1"/>
     </row>
-    <row r="3031" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3031" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3031" s="1"/>
     </row>
-    <row r="3032" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3032" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3032" s="1"/>
     </row>
-    <row r="3033" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3033" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3033" s="1"/>
     </row>
-    <row r="3034" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3034" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3034" s="1"/>
     </row>
-    <row r="3035" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3035" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3035" s="1"/>
     </row>
-    <row r="3036" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3036" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3036" s="1"/>
     </row>
-    <row r="3037" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3037" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3037" s="1"/>
     </row>
-    <row r="3038" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3038" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3038" s="1"/>
     </row>
-    <row r="3039" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3039" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3039" s="1"/>
     </row>
-    <row r="3040" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3040" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3040" s="1"/>
     </row>
     <row r="3041" spans="3:3" x14ac:dyDescent="0.25">
@@ -4215,52 +4468,53 @@
     <row r="3056" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3056" s="1"/>
     </row>
-    <row r="3057" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3057" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3057" s="1"/>
     </row>
-    <row r="3058" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3058" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3058" s="1"/>
     </row>
-    <row r="3059" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3059" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3059" s="1"/>
     </row>
-    <row r="3060" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3060" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3060" s="1"/>
-    </row>
-    <row r="3061" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3060" s="1"/>
+    </row>
+    <row r="3061" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3061" s="1"/>
     </row>
-    <row r="3062" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3062" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3062" s="1"/>
     </row>
-    <row r="3063" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3063" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3063" s="1"/>
     </row>
-    <row r="3064" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3064" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3064" s="1"/>
     </row>
-    <row r="3065" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3065" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3065" s="1"/>
     </row>
-    <row r="3066" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3066" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3066" s="1"/>
     </row>
-    <row r="3067" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3067" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3067" s="1"/>
     </row>
-    <row r="3068" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3068" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3068" s="1"/>
     </row>
-    <row r="3069" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3069" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3069" s="1"/>
     </row>
-    <row r="3070" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3070" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3070" s="1"/>
     </row>
-    <row r="3071" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3071" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3071" s="1"/>
     </row>
-    <row r="3072" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3072" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3072" s="1"/>
     </row>
     <row r="3073" spans="3:3" x14ac:dyDescent="0.25">
@@ -4311,198 +4565,198 @@
     <row r="3088" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3088" s="1"/>
     </row>
-    <row r="3089" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3089" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3089" s="1"/>
     </row>
-    <row r="3090" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3090" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3090" s="1"/>
     </row>
-    <row r="3091" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3091" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3091" s="1"/>
     </row>
-    <row r="3092" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3092" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3092" s="1"/>
-    </row>
-    <row r="3093" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3092" s="1"/>
+    </row>
+    <row r="3093" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3093" s="1"/>
     </row>
-    <row r="3094" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3094" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3094" s="1"/>
     </row>
-    <row r="3095" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3095" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3095" s="1"/>
     </row>
-    <row r="3096" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3096" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3096" s="1"/>
     </row>
-    <row r="3097" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3097" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3097" s="1"/>
     </row>
-    <row r="3098" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3098" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3098" s="1"/>
     </row>
-    <row r="3099" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3099" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3099" s="1"/>
     </row>
-    <row r="3100" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3100" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3100" s="1"/>
     </row>
-    <row r="3101" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3101" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3101" s="1"/>
     </row>
-    <row r="3102" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3102" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3102" s="1"/>
     </row>
-    <row r="3103" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3103" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3103" s="1"/>
     </row>
-    <row r="3104" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3104" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3104" s="1"/>
     </row>
-    <row r="3105" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3105" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3105" s="1"/>
     </row>
-    <row r="3106" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3106" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3106" s="1"/>
     </row>
-    <row r="3107" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3107" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3107" s="1"/>
-      <c r="D3107" s="1"/>
-    </row>
-    <row r="3108" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3108" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3108" s="1"/>
     </row>
-    <row r="3109" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3109" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3109" s="1"/>
     </row>
-    <row r="3110" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3110" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3110" s="1"/>
     </row>
-    <row r="3111" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3111" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3111" s="1"/>
     </row>
-    <row r="3112" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3112" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3112" s="1"/>
     </row>
-    <row r="3113" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3113" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3113" s="1"/>
     </row>
-    <row r="3114" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3114" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3114" s="1"/>
     </row>
-    <row r="3115" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3115" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3115" s="1"/>
     </row>
-    <row r="3116" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3116" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3116" s="1"/>
     </row>
-    <row r="3117" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3117" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3117" s="1"/>
     </row>
-    <row r="3118" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3118" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3118" s="1"/>
     </row>
-    <row r="3119" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3119" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3119" s="1"/>
     </row>
-    <row r="3120" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3120" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3120" s="1"/>
     </row>
-    <row r="3121" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3121" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3121" s="1"/>
     </row>
-    <row r="3122" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3122" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3122" s="1"/>
     </row>
-    <row r="3123" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3123" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3123" s="1"/>
     </row>
-    <row r="3124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3124" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3124" s="1"/>
     </row>
-    <row r="3125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3125" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3125" s="1"/>
-    </row>
-    <row r="3126" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3125" s="1"/>
+    </row>
+    <row r="3126" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3126" s="1"/>
     </row>
-    <row r="3127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3127" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3127" s="1"/>
     </row>
-    <row r="3128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3128" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3128" s="1"/>
     </row>
-    <row r="3129" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3129" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3129" s="1"/>
     </row>
-    <row r="3130" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3130" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3130" s="1"/>
     </row>
-    <row r="3131" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3131" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3131" s="1"/>
     </row>
-    <row r="3132" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3132" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3132" s="1"/>
     </row>
-    <row r="3133" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3133" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3133" s="1"/>
     </row>
-    <row r="3134" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3134" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3134" s="1"/>
     </row>
-    <row r="3135" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3135" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3135" s="1"/>
     </row>
-    <row r="3136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3136" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3136" s="1"/>
     </row>
-    <row r="3137" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3137" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3137" s="1"/>
     </row>
-    <row r="3138" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3138" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3138" s="1"/>
     </row>
-    <row r="3139" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3139" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3139" s="1"/>
-      <c r="D3139" s="1"/>
-    </row>
-    <row r="3140" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3140" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3140" s="1"/>
     </row>
-    <row r="3141" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3141" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3141" s="1"/>
     </row>
-    <row r="3142" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3142" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3142" s="1"/>
     </row>
-    <row r="3143" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3143" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3143" s="1"/>
     </row>
-    <row r="3144" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3144" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3144" s="1"/>
     </row>
-    <row r="3145" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3145" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3145" s="1"/>
     </row>
-    <row r="3146" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3146" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3146" s="1"/>
     </row>
-    <row r="3147" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3147" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3147" s="1"/>
     </row>
-    <row r="3148" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3148" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3148" s="1"/>
     </row>
-    <row r="3149" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3149" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3149" s="1"/>
     </row>
-    <row r="3150" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3150" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3150" s="1"/>
     </row>
-    <row r="3151" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3151" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3151" s="1"/>
     </row>
-    <row r="3152" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3152" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3152" s="1"/>
     </row>
     <row r="3153" spans="3:3" x14ac:dyDescent="0.25">
@@ -4553,53 +4807,52 @@
     <row r="3168" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3168" s="1"/>
     </row>
-    <row r="3169" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3169" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3169" s="1"/>
     </row>
-    <row r="3170" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3170" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3170" s="1"/>
     </row>
-    <row r="3171" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3171" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3171" s="1"/>
     </row>
-    <row r="3172" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3172" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3172" s="1"/>
-      <c r="D3172" s="1"/>
-    </row>
-    <row r="3173" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3173" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3173" s="1"/>
     </row>
-    <row r="3174" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3174" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3174" s="1"/>
     </row>
-    <row r="3175" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3175" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3175" s="1"/>
     </row>
-    <row r="3176" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3176" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3176" s="1"/>
     </row>
-    <row r="3177" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3177" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3177" s="1"/>
     </row>
-    <row r="3178" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3178" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3178" s="1"/>
     </row>
-    <row r="3179" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3179" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3179" s="1"/>
     </row>
-    <row r="3180" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3180" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3180" s="1"/>
     </row>
-    <row r="3181" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3181" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3181" s="1"/>
     </row>
-    <row r="3182" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3182" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3182" s="1"/>
     </row>
-    <row r="3183" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3183" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3183" s="1"/>
     </row>
-    <row r="3184" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3184" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3184" s="1"/>
     </row>
     <row r="3185" spans="3:3" x14ac:dyDescent="0.25">
@@ -4746,52 +4999,53 @@
     <row r="3232" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3232" s="1"/>
     </row>
-    <row r="3233" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3233" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3233" s="1"/>
     </row>
-    <row r="3234" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3234" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3234" s="1"/>
     </row>
-    <row r="3235" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3235" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3235" s="1"/>
     </row>
-    <row r="3236" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3236" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3236" s="1"/>
     </row>
-    <row r="3237" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3237" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3237" s="1"/>
     </row>
-    <row r="3238" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3238" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3238" s="1"/>
     </row>
-    <row r="3239" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3239" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3239" s="1"/>
     </row>
-    <row r="3240" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3240" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3240" s="1"/>
     </row>
-    <row r="3241" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3241" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3241" s="1"/>
     </row>
-    <row r="3242" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3242" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3242" s="1"/>
     </row>
-    <row r="3243" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3243" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3243" s="1"/>
     </row>
-    <row r="3244" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3244" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3244" s="1"/>
     </row>
-    <row r="3245" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3245" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3245" s="1"/>
     </row>
-    <row r="3246" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3246" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3246" s="1"/>
-    </row>
-    <row r="3247" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3246" s="1"/>
+    </row>
+    <row r="3247" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3247" s="1"/>
     </row>
-    <row r="3248" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3248" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3248" s="1"/>
     </row>
     <row r="3249" spans="3:3" x14ac:dyDescent="0.25">
@@ -4842,101 +5096,103 @@
     <row r="3264" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3264" s="1"/>
     </row>
-    <row r="3265" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3265" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3265" s="1"/>
     </row>
-    <row r="3266" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3266" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3266" s="1"/>
     </row>
-    <row r="3267" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3267" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3267" s="1"/>
     </row>
-    <row r="3268" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3268" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3268" s="1"/>
     </row>
-    <row r="3269" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3269" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3269" s="1"/>
     </row>
-    <row r="3270" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3270" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3270" s="1"/>
     </row>
-    <row r="3271" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3271" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3271" s="1"/>
     </row>
-    <row r="3272" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3272" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3272" s="1"/>
-    </row>
-    <row r="3273" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3272" s="1"/>
+    </row>
+    <row r="3273" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3273" s="1"/>
     </row>
-    <row r="3274" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3274" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3274" s="1"/>
-    </row>
-    <row r="3275" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3274" s="1"/>
+    </row>
+    <row r="3275" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3275" s="1"/>
     </row>
-    <row r="3276" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3276" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3276" s="1"/>
     </row>
-    <row r="3277" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3277" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3277" s="1"/>
     </row>
-    <row r="3278" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3278" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3278" s="1"/>
     </row>
-    <row r="3279" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3279" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3279" s="1"/>
     </row>
-    <row r="3280" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3280" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3280" s="1"/>
-    </row>
-    <row r="3281" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D3280" s="1"/>
+    </row>
+    <row r="3281" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3281" s="1"/>
     </row>
-    <row r="3282" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3282" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3282" s="1"/>
     </row>
-    <row r="3283" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3283" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3283" s="1"/>
     </row>
-    <row r="3284" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3284" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3284" s="1"/>
     </row>
-    <row r="3285" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3285" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3285" s="1"/>
     </row>
-    <row r="3286" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3286" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3286" s="1"/>
     </row>
-    <row r="3287" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3287" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3287" s="1"/>
     </row>
-    <row r="3288" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3288" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3288" s="1"/>
     </row>
-    <row r="3289" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3289" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3289" s="1"/>
     </row>
-    <row r="3290" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3290" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3290" s="1"/>
     </row>
-    <row r="3291" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3291" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3291" s="1"/>
     </row>
-    <row r="3292" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3292" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3292" s="1"/>
     </row>
-    <row r="3293" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3293" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3293" s="1"/>
-      <c r="D3293" s="1"/>
-    </row>
-    <row r="3294" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3294" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3294" s="1"/>
     </row>
-    <row r="3295" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3295" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3295" s="1"/>
     </row>
-    <row r="3296" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3296" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3296" s="1"/>
     </row>
     <row r="3297" spans="3:3" x14ac:dyDescent="0.25">
@@ -4987,103 +5243,101 @@
     <row r="3312" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3312" s="1"/>
     </row>
-    <row r="3313" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3313" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3313" s="1"/>
     </row>
-    <row r="3314" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3314" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3314" s="1"/>
     </row>
-    <row r="3315" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3315" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3315" s="1"/>
     </row>
-    <row r="3316" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3316" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3316" s="1"/>
     </row>
-    <row r="3317" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3317" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3317" s="1"/>
     </row>
-    <row r="3318" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3318" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3318" s="1"/>
     </row>
-    <row r="3319" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3319" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3319" s="1"/>
-      <c r="D3319" s="1"/>
-    </row>
-    <row r="3320" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3320" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3320" s="1"/>
     </row>
-    <row r="3321" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3321" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3321" s="1"/>
-      <c r="D3321" s="1"/>
-    </row>
-    <row r="3322" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3322" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3322" s="1"/>
     </row>
-    <row r="3323" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3323" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3323" s="1"/>
     </row>
-    <row r="3324" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3324" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3324" s="1"/>
     </row>
-    <row r="3325" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3325" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3325" s="1"/>
     </row>
-    <row r="3326" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3326" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3326" s="1"/>
     </row>
-    <row r="3327" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3327" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3327" s="1"/>
-      <c r="D3327" s="1"/>
-    </row>
-    <row r="3328" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3328" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3328" s="1"/>
     </row>
-    <row r="3329" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3329" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3329" s="1"/>
     </row>
-    <row r="3330" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3330" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3330" s="1"/>
     </row>
-    <row r="3331" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3331" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3331" s="1"/>
     </row>
-    <row r="3332" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3332" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3332" s="1"/>
     </row>
-    <row r="3333" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3333" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3333" s="1"/>
-    </row>
-    <row r="3334" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3333" s="1"/>
+    </row>
+    <row r="3334" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3334" s="1"/>
     </row>
-    <row r="3335" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3335" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3335" s="1"/>
     </row>
-    <row r="3336" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3336" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3336" s="1"/>
     </row>
-    <row r="3337" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3337" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3337" s="1"/>
     </row>
-    <row r="3338" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3338" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3338" s="1"/>
     </row>
-    <row r="3339" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3339" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3339" s="1"/>
     </row>
-    <row r="3340" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3340" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3340" s="1"/>
     </row>
-    <row r="3341" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3341" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3341" s="1"/>
     </row>
-    <row r="3342" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3342" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3342" s="1"/>
     </row>
-    <row r="3343" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3343" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3343" s="1"/>
     </row>
-    <row r="3344" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3344" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3344" s="1"/>
     </row>
     <row r="3345" spans="3:3" x14ac:dyDescent="0.25">
@@ -5182,53 +5436,52 @@
     <row r="3376" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3376" s="1"/>
     </row>
-    <row r="3377" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3377" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3377" s="1"/>
     </row>
-    <row r="3378" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3378" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3378" s="1"/>
     </row>
-    <row r="3379" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3379" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3379" s="1"/>
     </row>
-    <row r="3380" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3380" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3380" s="1"/>
-      <c r="D3380" s="1"/>
-    </row>
-    <row r="3381" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3381" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3381" s="1"/>
     </row>
-    <row r="3382" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3382" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3382" s="1"/>
     </row>
-    <row r="3383" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3383" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3383" s="1"/>
     </row>
-    <row r="3384" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3384" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3384" s="1"/>
     </row>
-    <row r="3385" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3385" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3385" s="1"/>
     </row>
-    <row r="3386" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3386" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3386" s="1"/>
     </row>
-    <row r="3387" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3387" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3387" s="1"/>
     </row>
-    <row r="3388" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3388" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3388" s="1"/>
     </row>
-    <row r="3389" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3389" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3389" s="1"/>
     </row>
-    <row r="3390" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3390" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3390" s="1"/>
     </row>
-    <row r="3391" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3391" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3391" s="1"/>
     </row>
-    <row r="3392" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3392" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3392" s="1"/>
     </row>
     <row r="3393" spans="3:3" x14ac:dyDescent="0.25">
@@ -5327,52 +5580,53 @@
     <row r="3424" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3424" s="1"/>
     </row>
-    <row r="3425" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3425" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3425" s="1"/>
     </row>
-    <row r="3426" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3426" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3426" s="1"/>
     </row>
-    <row r="3427" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3427" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3427" s="1"/>
     </row>
-    <row r="3428" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3428" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3428" s="1"/>
     </row>
-    <row r="3429" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3429" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3429" s="1"/>
     </row>
-    <row r="3430" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3430" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3430" s="1"/>
     </row>
-    <row r="3431" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3431" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3431" s="1"/>
     </row>
-    <row r="3432" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3432" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3432" s="1"/>
     </row>
-    <row r="3433" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3433" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3433" s="1"/>
     </row>
-    <row r="3434" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3434" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3434" s="1"/>
     </row>
-    <row r="3435" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3435" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3435" s="1"/>
     </row>
-    <row r="3436" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3436" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3436" s="1"/>
     </row>
-    <row r="3437" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3437" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3437" s="1"/>
-    </row>
-    <row r="3438" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3437" s="1"/>
+    </row>
+    <row r="3438" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3438" s="1"/>
     </row>
-    <row r="3439" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3439" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3439" s="1"/>
     </row>
-    <row r="3440" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3440" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3440" s="1"/>
     </row>
     <row r="3441" spans="3:3" x14ac:dyDescent="0.25">
@@ -5485,6 +5739,7 @@
     </row>
     <row r="3477" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3477" s="1"/>
+      <c r="D3477" s="1"/>
     </row>
     <row r="3478" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3478" s="1"/>
@@ -5506,7 +5761,6 @@
     </row>
     <row r="3484" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3484" s="1"/>
-      <c r="D3484" s="1"/>
     </row>
     <row r="3485" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3485" s="1"/>
@@ -5568,101 +5822,101 @@
     <row r="3504" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3504" s="1"/>
     </row>
-    <row r="3505" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3505" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3505" s="1"/>
     </row>
-    <row r="3506" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3506" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3506" s="1"/>
     </row>
-    <row r="3507" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3507" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3507" s="1"/>
     </row>
-    <row r="3508" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3508" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3508" s="1"/>
     </row>
-    <row r="3509" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3509" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3509" s="1"/>
-    </row>
-    <row r="3510" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3509" s="1"/>
+    </row>
+    <row r="3510" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3510" s="1"/>
     </row>
-    <row r="3511" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3511" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3511" s="1"/>
     </row>
-    <row r="3512" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3512" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3512" s="1"/>
     </row>
-    <row r="3513" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3513" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3513" s="1"/>
     </row>
-    <row r="3514" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3514" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3514" s="1"/>
     </row>
-    <row r="3515" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3515" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3515" s="1"/>
     </row>
-    <row r="3516" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3516" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3516" s="1"/>
     </row>
-    <row r="3517" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3517" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3517" s="1"/>
     </row>
-    <row r="3518" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3518" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3518" s="1"/>
     </row>
-    <row r="3519" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3519" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3519" s="1"/>
     </row>
-    <row r="3520" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3520" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3520" s="1"/>
     </row>
-    <row r="3521" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3521" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3521" s="1"/>
     </row>
-    <row r="3522" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3522" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3522" s="1"/>
     </row>
-    <row r="3523" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3523" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3523" s="1"/>
     </row>
-    <row r="3524" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3524" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3524" s="1"/>
-      <c r="D3524" s="1"/>
-    </row>
-    <row r="3525" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3525" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3525" s="1"/>
     </row>
-    <row r="3526" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3526" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3526" s="1"/>
     </row>
-    <row r="3527" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3527" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3527" s="1"/>
     </row>
-    <row r="3528" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3528" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3528" s="1"/>
     </row>
-    <row r="3529" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3529" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3529" s="1"/>
     </row>
-    <row r="3530" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3530" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3530" s="1"/>
     </row>
-    <row r="3531" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3531" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3531" s="1"/>
     </row>
-    <row r="3532" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3532" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3532" s="1"/>
     </row>
-    <row r="3533" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3533" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3533" s="1"/>
     </row>
-    <row r="3534" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3534" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3534" s="1"/>
     </row>
-    <row r="3535" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3535" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3535" s="1"/>
     </row>
-    <row r="3536" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3536" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3536" s="1"/>
     </row>
     <row r="3537" spans="3:3" x14ac:dyDescent="0.25">
@@ -5713,53 +5967,52 @@
     <row r="3552" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3552" s="1"/>
     </row>
-    <row r="3553" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3553" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3553" s="1"/>
     </row>
-    <row r="3554" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3554" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3554" s="1"/>
     </row>
-    <row r="3555" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3555" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3555" s="1"/>
     </row>
-    <row r="3556" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3556" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3556" s="1"/>
-      <c r="D3556" s="1"/>
-    </row>
-    <row r="3557" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3557" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3557" s="1"/>
     </row>
-    <row r="3558" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3558" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3558" s="1"/>
     </row>
-    <row r="3559" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3559" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3559" s="1"/>
     </row>
-    <row r="3560" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3560" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3560" s="1"/>
     </row>
-    <row r="3561" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3561" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3561" s="1"/>
     </row>
-    <row r="3562" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3562" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3562" s="1"/>
     </row>
-    <row r="3563" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3563" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3563" s="1"/>
     </row>
-    <row r="3564" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3564" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3564" s="1"/>
     </row>
-    <row r="3565" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3565" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3565" s="1"/>
     </row>
-    <row r="3566" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3566" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3566" s="1"/>
     </row>
-    <row r="3567" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3567" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3567" s="1"/>
     </row>
-    <row r="3568" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3568" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3568" s="1"/>
     </row>
     <row r="3569" spans="3:3" x14ac:dyDescent="0.25">
@@ -5858,52 +6111,53 @@
     <row r="3600" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3600" s="1"/>
     </row>
-    <row r="3601" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3601" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3601" s="1"/>
     </row>
-    <row r="3602" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3602" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3602" s="1"/>
     </row>
-    <row r="3603" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3603" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3603" s="1"/>
     </row>
-    <row r="3604" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3604" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3604" s="1"/>
     </row>
-    <row r="3605" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3605" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3605" s="1"/>
     </row>
-    <row r="3606" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3606" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3606" s="1"/>
     </row>
-    <row r="3607" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3607" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3607" s="1"/>
     </row>
-    <row r="3608" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3608" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3608" s="1"/>
     </row>
-    <row r="3609" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3609" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3609" s="1"/>
-    </row>
-    <row r="3610" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3609" s="1"/>
+    </row>
+    <row r="3610" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3610" s="1"/>
     </row>
-    <row r="3611" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3611" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3611" s="1"/>
     </row>
-    <row r="3612" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3612" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3612" s="1"/>
     </row>
-    <row r="3613" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3613" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3613" s="1"/>
     </row>
-    <row r="3614" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3614" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3614" s="1"/>
     </row>
-    <row r="3615" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3615" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3615" s="1"/>
     </row>
-    <row r="3616" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3616" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3616" s="1"/>
     </row>
     <row r="3617" spans="3:3" x14ac:dyDescent="0.25">
@@ -5954,52 +6208,53 @@
     <row r="3632" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3632" s="1"/>
     </row>
-    <row r="3633" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3633" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3633" s="1"/>
     </row>
-    <row r="3634" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3634" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3634" s="1"/>
     </row>
-    <row r="3635" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3635" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3635" s="1"/>
     </row>
-    <row r="3636" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3636" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3636" s="1"/>
     </row>
-    <row r="3637" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3637" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3637" s="1"/>
     </row>
-    <row r="3638" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3638" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3638" s="1"/>
     </row>
-    <row r="3639" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3639" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3639" s="1"/>
     </row>
-    <row r="3640" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3640" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3640" s="1"/>
     </row>
-    <row r="3641" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3641" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3641" s="1"/>
-    </row>
-    <row r="3642" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3641" s="1"/>
+    </row>
+    <row r="3642" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3642" s="1"/>
     </row>
-    <row r="3643" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3643" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3643" s="1"/>
     </row>
-    <row r="3644" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3644" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3644" s="1"/>
     </row>
-    <row r="3645" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3645" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3645" s="1"/>
     </row>
-    <row r="3646" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3646" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3646" s="1"/>
     </row>
-    <row r="3647" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3647" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3647" s="1"/>
     </row>
-    <row r="3648" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3648" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3648" s="1"/>
     </row>
     <row r="3649" spans="3:4" x14ac:dyDescent="0.25">
@@ -6007,12 +6262,14 @@
     </row>
     <row r="3650" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3650" s="1"/>
+      <c r="D3650" s="1"/>
     </row>
     <row r="3651" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3651" s="1"/>
     </row>
     <row r="3652" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3652" s="1"/>
+      <c r="D3652" s="1"/>
     </row>
     <row r="3653" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3653" s="1"/>
@@ -6025,7 +6282,6 @@
     </row>
     <row r="3656" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3656" s="1"/>
-      <c r="D3656" s="1"/>
     </row>
     <row r="3657" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3657" s="1"/>
@@ -6051,56 +6307,61 @@
     <row r="3664" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3664" s="1"/>
     </row>
-    <row r="3665" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3665" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3665" s="1"/>
-    </row>
-    <row r="3666" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3665" s="1"/>
+    </row>
+    <row r="3666" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3666" s="1"/>
     </row>
-    <row r="3667" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3667" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3667" s="1"/>
     </row>
-    <row r="3668" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3668" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3668" s="1"/>
-    </row>
-    <row r="3669" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3668" s="1"/>
+    </row>
+    <row r="3669" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3669" s="1"/>
     </row>
-    <row r="3670" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3670" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3670" s="1"/>
     </row>
-    <row r="3671" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3671" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3671" s="1"/>
     </row>
-    <row r="3672" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3672" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3672" s="1"/>
-    </row>
-    <row r="3673" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3672" s="1"/>
+    </row>
+    <row r="3673" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3673" s="1"/>
     </row>
-    <row r="3674" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3674" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3674" s="1"/>
     </row>
-    <row r="3675" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3675" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3675" s="1"/>
-    </row>
-    <row r="3676" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3675" s="1"/>
+    </row>
+    <row r="3676" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3676" s="1"/>
     </row>
-    <row r="3677" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3677" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3677" s="1"/>
     </row>
-    <row r="3678" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3678" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3678" s="1"/>
     </row>
-    <row r="3679" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3679" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3679" s="1"/>
     </row>
-    <row r="3680" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3680" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3680" s="1"/>
     </row>
     <row r="3681" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3681" s="1"/>
+      <c r="D3681" s="1"/>
     </row>
     <row r="3682" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3682" s="1"/>
@@ -6110,6 +6371,7 @@
     </row>
     <row r="3684" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3684" s="1"/>
+      <c r="D3684" s="1"/>
     </row>
     <row r="3685" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3685" s="1"/>
@@ -6122,167 +6384,12 @@
     </row>
     <row r="3688" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3688" s="1"/>
-      <c r="D3688" s="1"/>
     </row>
     <row r="3689" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3689" s="1"/>
-    </row>
-    <row r="3690" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3690" s="1"/>
-    </row>
-    <row r="3691" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3691" s="1"/>
-    </row>
-    <row r="3692" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3692" s="1"/>
-    </row>
-    <row r="3693" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3693" s="1"/>
-    </row>
-    <row r="3694" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3694" s="1"/>
-    </row>
-    <row r="3695" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3695" s="1"/>
-    </row>
-    <row r="3696" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3696" s="1"/>
-    </row>
-    <row r="3697" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3697" s="1"/>
-      <c r="D3697" s="1"/>
-    </row>
-    <row r="3698" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3698" s="1"/>
-    </row>
-    <row r="3699" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3699" s="1"/>
-      <c r="D3699" s="1"/>
-    </row>
-    <row r="3700" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3700" s="1"/>
-    </row>
-    <row r="3701" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3701" s="1"/>
-    </row>
-    <row r="3702" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3702" s="1"/>
-    </row>
-    <row r="3703" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3703" s="1"/>
-    </row>
-    <row r="3704" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3704" s="1"/>
-    </row>
-    <row r="3705" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3705" s="1"/>
-    </row>
-    <row r="3706" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3706" s="1"/>
-    </row>
-    <row r="3707" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3707" s="1"/>
-    </row>
-    <row r="3708" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3708" s="1"/>
-    </row>
-    <row r="3709" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3709" s="1"/>
-    </row>
-    <row r="3710" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3710" s="1"/>
-    </row>
-    <row r="3711" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3711" s="1"/>
-    </row>
-    <row r="3712" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3712" s="1"/>
-      <c r="D3712" s="1"/>
-    </row>
-    <row r="3713" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3713" s="1"/>
-    </row>
-    <row r="3714" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3714" s="1"/>
-    </row>
-    <row r="3715" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3715" s="1"/>
-      <c r="D3715" s="1"/>
-    </row>
-    <row r="3716" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3716" s="1"/>
-    </row>
-    <row r="3717" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3717" s="1"/>
-    </row>
-    <row r="3718" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3718" s="1"/>
-    </row>
-    <row r="3719" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3719" s="1"/>
-      <c r="D3719" s="1"/>
-    </row>
-    <row r="3720" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3720" s="1"/>
-    </row>
-    <row r="3721" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3721" s="1"/>
-    </row>
-    <row r="3722" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3722" s="1"/>
-      <c r="D3722" s="1"/>
-    </row>
-    <row r="3723" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3723" s="1"/>
-    </row>
-    <row r="3724" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3724" s="1"/>
-    </row>
-    <row r="3725" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3725" s="1"/>
-    </row>
-    <row r="3726" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3726" s="1"/>
-    </row>
-    <row r="3727" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3727" s="1"/>
-    </row>
-    <row r="3728" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3728" s="1"/>
-      <c r="D3728" s="1"/>
-    </row>
-    <row r="3729" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3729" s="1"/>
-    </row>
-    <row r="3730" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3730" s="1"/>
-    </row>
-    <row r="3731" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3731" s="1"/>
-      <c r="D3731" s="1"/>
-    </row>
-    <row r="3732" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3732" s="1"/>
-    </row>
-    <row r="3733" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3733" s="1"/>
-    </row>
-    <row r="3734" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3734" s="1"/>
-    </row>
-    <row r="3735" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3735" s="1"/>
-    </row>
-    <row r="3736" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3736" s="1"/>
-      <c r="D3736" s="1"/>
+      <c r="D3689" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C31" xr:uid="{11BDB550-E1E7-404D-B978-F462E546FC21}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C34">
-      <sortCondition ref="B1:B31"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/SeguimientoCeldas.xlsx
+++ b/data/SeguimientoCeldas.xlsx
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Documents\project\ubuntu\dashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\project\ubuntu\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1CD06E-B146-440C-A11F-8B32C7FDA522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB6EAD4-9D84-4864-A3D7-DCFC99D77110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Seguimiento" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>CellName</t>
   </si>
@@ -227,6 +227,48 @@
   </si>
   <si>
     <t>Pendiente Trabajos Infraestructura</t>
+  </si>
+  <si>
+    <t>COL_EINSTEIN1</t>
+  </si>
+  <si>
+    <t>COL_EINSTEIN2</t>
+  </si>
+  <si>
+    <t>COL_EINSTEIN3</t>
+  </si>
+  <si>
+    <t>PI_UIO_COL_EINSTEIN_2</t>
+  </si>
+  <si>
+    <t>PI_UIO_COL_EINSTEIN_3</t>
+  </si>
+  <si>
+    <t>44221-2</t>
+  </si>
+  <si>
+    <t>44221-3</t>
+  </si>
+  <si>
+    <t>ORE_JOY_JOYA_DE_LOS_SACHAS_L21_3</t>
+  </si>
+  <si>
+    <t>44863-3</t>
+  </si>
+  <si>
+    <t>Daño en RRU</t>
+  </si>
+  <si>
+    <t>MOR_TAISHA_HUAWEI1</t>
+  </si>
+  <si>
+    <t>MOR_TAISHA_HUAWEI2</t>
+  </si>
+  <si>
+    <t>MOR_TAISHA_HUAWEI3</t>
+  </si>
+  <si>
+    <t>Celda Bloqueada</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BDB550-E1E7-404D-B978-F462E546FC21}">
-  <dimension ref="A1:D3689"/>
+  <dimension ref="A1:D3694"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
@@ -1517,10 +1559,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="B41">
+        <v>42211</v>
       </c>
       <c r="C41" t="s">
         <v>37</v>
@@ -1528,76 +1570,76 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B42">
-        <v>32801</v>
+        <v>42212</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B43">
-        <v>42481</v>
+        <v>42213</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44">
-        <v>42482</v>
+        <v>72</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>42483</v>
+        <v>71</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46">
-        <v>41481</v>
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="B47">
+        <v>32801</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B48">
-        <v>32061</v>
+        <v>42481</v>
       </c>
       <c r="C48" t="s">
         <v>26</v>
@@ -1605,54 +1647,54 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B49">
-        <v>49574</v>
+        <v>42482</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B50">
-        <v>49575</v>
+        <v>42483</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B51">
-        <v>46031</v>
+        <v>41481</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52">
-        <v>46032</v>
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B53">
-        <v>46033</v>
+        <v>32061</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -1660,61 +1702,145 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B54">
-        <v>46038</v>
+        <v>49574</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55">
+        <v>49575</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56">
+        <v>46031</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57">
+        <v>46032</v>
+      </c>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58">
+        <v>46033</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>46038</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>43</v>
       </c>
-      <c r="B55">
+      <c r="B60">
         <v>46039</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C60" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="1002" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1002" s="1"/>
-    </row>
-    <row r="1141" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1141" s="1"/>
-    </row>
-    <row r="1333" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1333" s="1"/>
-    </row>
-    <row r="1517" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1517" s="1"/>
-    </row>
-    <row r="1571" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1571" s="1"/>
-    </row>
-    <row r="1649" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1649" s="1"/>
-    </row>
-    <row r="2055" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2055" s="1"/>
-    </row>
-    <row r="2137" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2137" s="1"/>
-    </row>
-    <row r="2138" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2138" s="1"/>
-    </row>
-    <row r="2139" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2139" s="1"/>
-    </row>
-    <row r="2140" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2140" s="1"/>
-    </row>
-    <row r="2141" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2141" s="1"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62">
+        <v>48741</v>
+      </c>
+      <c r="C62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63">
+        <v>48742</v>
+      </c>
+      <c r="C63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64">
+        <v>48743</v>
+      </c>
+      <c r="C64" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1007" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1007" s="1"/>
+    </row>
+    <row r="1146" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1146" s="1"/>
+    </row>
+    <row r="1338" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1338" s="1"/>
+    </row>
+    <row r="1522" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1522" s="1"/>
+    </row>
+    <row r="1576" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1576" s="1"/>
+    </row>
+    <row r="1654" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1654" s="1"/>
+    </row>
+    <row r="2060" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D2060" s="1"/>
     </row>
     <row r="2142" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2142" s="1"/>
@@ -1821,101 +1947,101 @@
     <row r="2176" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2176" s="1"/>
     </row>
-    <row r="2177" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2177" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2177" s="1"/>
     </row>
-    <row r="2178" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2178" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2178" s="1"/>
     </row>
-    <row r="2179" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2179" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2179" s="1"/>
     </row>
-    <row r="2180" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2180" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2180" s="1"/>
     </row>
-    <row r="2181" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2181" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2181" s="1"/>
     </row>
-    <row r="2182" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2182" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2182" s="1"/>
     </row>
-    <row r="2183" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2183" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2183" s="1"/>
     </row>
-    <row r="2184" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2184" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2184" s="1"/>
     </row>
-    <row r="2185" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2185" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2185" s="1"/>
     </row>
-    <row r="2186" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2186" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2186" s="1"/>
     </row>
-    <row r="2187" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2187" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2187" s="1"/>
     </row>
-    <row r="2188" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2188" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2188" s="1"/>
     </row>
-    <row r="2189" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2189" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2189" s="1"/>
     </row>
-    <row r="2190" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2190" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2190" s="1"/>
     </row>
-    <row r="2191" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2191" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2191" s="1"/>
     </row>
-    <row r="2192" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2192" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2192" s="1"/>
-      <c r="D2192" s="1"/>
-    </row>
-    <row r="2193" spans="3:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2193" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2193" s="1"/>
     </row>
-    <row r="2194" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2194" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2194" s="1"/>
     </row>
-    <row r="2195" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2195" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2195" s="1"/>
     </row>
-    <row r="2196" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2196" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2196" s="1"/>
     </row>
-    <row r="2197" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2197" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2197" s="1"/>
-    </row>
-    <row r="2198" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2197" s="1"/>
+    </row>
+    <row r="2198" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2198" s="1"/>
     </row>
-    <row r="2199" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2199" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2199" s="1"/>
     </row>
-    <row r="2200" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2200" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2200" s="1"/>
     </row>
-    <row r="2201" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2201" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2201" s="1"/>
     </row>
-    <row r="2202" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2202" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2202" s="1"/>
     </row>
-    <row r="2203" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2203" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2203" s="1"/>
     </row>
-    <row r="2204" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2204" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2204" s="1"/>
     </row>
-    <row r="2205" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2205" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2205" s="1"/>
     </row>
-    <row r="2206" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2206" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2206" s="1"/>
     </row>
-    <row r="2207" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2207" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2207" s="1"/>
     </row>
-    <row r="2208" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2208" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2208" s="1"/>
     </row>
     <row r="2209" spans="3:3" x14ac:dyDescent="0.25">
@@ -1963,6 +2089,9 @@
     <row r="2223" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2223" s="1"/>
     </row>
+    <row r="2224" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2224" s="1"/>
+    </row>
     <row r="2225" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2225" s="1"/>
     </row>
@@ -1975,9 +2104,6 @@
     <row r="2228" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2228" s="1"/>
     </row>
-    <row r="2229" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2229" s="1"/>
-    </row>
     <row r="2230" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2230" s="1"/>
     </row>
@@ -2373,7 +2499,6 @@
     </row>
     <row r="2361" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2361" s="1"/>
-      <c r="D2361" s="1"/>
     </row>
     <row r="2362" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2362" s="1"/>
@@ -2389,6 +2514,7 @@
     </row>
     <row r="2366" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2366" s="1"/>
+      <c r="D2366" s="1"/>
     </row>
     <row r="2367" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2367" s="1"/>
@@ -2396,101 +2522,101 @@
     <row r="2368" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2368" s="1"/>
     </row>
-    <row r="2369" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2369" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2369" s="1"/>
     </row>
-    <row r="2370" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2370" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2370" s="1"/>
     </row>
-    <row r="2371" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2371" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2371" s="1"/>
     </row>
-    <row r="2372" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2372" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2372" s="1"/>
     </row>
-    <row r="2373" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2373" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2373" s="1"/>
     </row>
-    <row r="2374" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2374" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2374" s="1"/>
     </row>
-    <row r="2375" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2375" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2375" s="1"/>
     </row>
-    <row r="2376" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2376" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2376" s="1"/>
     </row>
-    <row r="2377" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2377" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2377" s="1"/>
     </row>
-    <row r="2378" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2378" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2378" s="1"/>
     </row>
-    <row r="2379" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2379" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2379" s="1"/>
     </row>
-    <row r="2380" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2380" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2380" s="1"/>
     </row>
-    <row r="2381" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2381" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2381" s="1"/>
     </row>
-    <row r="2382" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2382" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2382" s="1"/>
     </row>
-    <row r="2383" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2383" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2383" s="1"/>
     </row>
-    <row r="2384" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2384" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2384" s="1"/>
-      <c r="D2384" s="1"/>
-    </row>
-    <row r="2385" spans="3:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2385" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2385" s="1"/>
     </row>
-    <row r="2386" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2386" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2386" s="1"/>
     </row>
-    <row r="2387" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2387" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2387" s="1"/>
     </row>
-    <row r="2388" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2388" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2388" s="1"/>
     </row>
-    <row r="2389" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2389" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2389" s="1"/>
-    </row>
-    <row r="2390" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2389" s="1"/>
+    </row>
+    <row r="2390" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2390" s="1"/>
     </row>
-    <row r="2391" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2391" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2391" s="1"/>
     </row>
-    <row r="2392" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2392" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2392" s="1"/>
     </row>
-    <row r="2393" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2393" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2393" s="1"/>
     </row>
-    <row r="2394" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2394" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2394" s="1"/>
     </row>
-    <row r="2395" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2395" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2395" s="1"/>
     </row>
-    <row r="2396" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2396" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2396" s="1"/>
     </row>
-    <row r="2397" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2397" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2397" s="1"/>
     </row>
-    <row r="2398" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2398" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2398" s="1"/>
     </row>
-    <row r="2399" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2399" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2399" s="1"/>
     </row>
-    <row r="2400" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2400" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2400" s="1"/>
     </row>
     <row r="2401" spans="3:3" x14ac:dyDescent="0.25">
@@ -3053,7 +3179,6 @@
     </row>
     <row r="2587" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2587" s="1"/>
-      <c r="D2587" s="1"/>
     </row>
     <row r="2588" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2588" s="1"/>
@@ -3069,6 +3194,7 @@
     </row>
     <row r="2592" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2592" s="1"/>
+      <c r="D2592" s="1"/>
     </row>
     <row r="2593" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2593" s="1"/>
@@ -3147,7 +3273,6 @@
     </row>
     <row r="2618" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2618" s="1"/>
-      <c r="D2618" s="1"/>
     </row>
     <row r="2619" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2619" s="1"/>
@@ -3163,6 +3288,7 @@
     </row>
     <row r="2623" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2623" s="1"/>
+      <c r="D2623" s="1"/>
     </row>
     <row r="2624" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2624" s="1"/>
@@ -3583,7 +3709,6 @@
     </row>
     <row r="2763" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2763" s="1"/>
-      <c r="D2763" s="1"/>
     </row>
     <row r="2764" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2764" s="1"/>
@@ -3599,6 +3724,7 @@
     </row>
     <row r="2768" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2768" s="1"/>
+      <c r="D2768" s="1"/>
     </row>
     <row r="2769" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2769" s="1"/>
@@ -3824,7 +3950,6 @@
     </row>
     <row r="2843" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2843" s="1"/>
-      <c r="D2843" s="1"/>
     </row>
     <row r="2844" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2844" s="1"/>
@@ -3840,6 +3965,7 @@
     </row>
     <row r="2848" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2848" s="1"/>
+      <c r="D2848" s="1"/>
     </row>
     <row r="2849" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2849" s="1"/>
@@ -3889,101 +4015,101 @@
     <row r="2864" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2864" s="1"/>
     </row>
-    <row r="2865" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2865" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2865" s="1"/>
     </row>
-    <row r="2866" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2866" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2866" s="1"/>
     </row>
-    <row r="2867" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2867" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2867" s="1"/>
     </row>
-    <row r="2868" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2868" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2868" s="1"/>
     </row>
-    <row r="2869" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2869" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2869" s="1"/>
     </row>
-    <row r="2870" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2870" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2870" s="1"/>
     </row>
-    <row r="2871" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2871" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2871" s="1"/>
     </row>
-    <row r="2872" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2872" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2872" s="1"/>
     </row>
-    <row r="2873" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2873" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2873" s="1"/>
     </row>
-    <row r="2874" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2874" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2874" s="1"/>
     </row>
-    <row r="2875" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2875" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2875" s="1"/>
     </row>
-    <row r="2876" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2876" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2876" s="1"/>
     </row>
-    <row r="2877" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2877" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2877" s="1"/>
     </row>
-    <row r="2878" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2878" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2878" s="1"/>
-      <c r="D2878" s="1"/>
-    </row>
-    <row r="2879" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2879" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2879" s="1"/>
     </row>
-    <row r="2880" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2880" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2880" s="1"/>
     </row>
-    <row r="2881" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2881" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2881" s="1"/>
     </row>
-    <row r="2882" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2882" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2882" s="1"/>
     </row>
-    <row r="2883" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2883" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2883" s="1"/>
-    </row>
-    <row r="2884" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2883" s="1"/>
+    </row>
+    <row r="2884" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2884" s="1"/>
     </row>
-    <row r="2885" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2885" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2885" s="1"/>
     </row>
-    <row r="2886" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2886" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2886" s="1"/>
     </row>
-    <row r="2887" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2887" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2887" s="1"/>
     </row>
-    <row r="2888" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2888" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2888" s="1"/>
     </row>
-    <row r="2889" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2889" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2889" s="1"/>
     </row>
-    <row r="2890" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2890" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2890" s="1"/>
     </row>
-    <row r="2891" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2891" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2891" s="1"/>
     </row>
-    <row r="2892" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2892" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2892" s="1"/>
     </row>
-    <row r="2893" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2893" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2893" s="1"/>
     </row>
-    <row r="2894" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2894" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2894" s="1"/>
     </row>
-    <row r="2895" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2895" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2895" s="1"/>
     </row>
-    <row r="2896" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2896" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2896" s="1"/>
     </row>
     <row r="2897" spans="3:3" x14ac:dyDescent="0.25">
@@ -4082,101 +4208,101 @@
     <row r="2928" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2928" s="1"/>
     </row>
-    <row r="2929" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2929" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2929" s="1"/>
     </row>
-    <row r="2930" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2930" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2930" s="1"/>
     </row>
-    <row r="2931" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2931" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2931" s="1"/>
     </row>
-    <row r="2932" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2932" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2932" s="1"/>
     </row>
-    <row r="2933" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2933" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2933" s="1"/>
     </row>
-    <row r="2934" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2934" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2934" s="1"/>
     </row>
-    <row r="2935" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2935" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2935" s="1"/>
     </row>
-    <row r="2936" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2936" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2936" s="1"/>
     </row>
-    <row r="2937" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2937" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2937" s="1"/>
     </row>
-    <row r="2938" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2938" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2938" s="1"/>
     </row>
-    <row r="2939" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2939" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2939" s="1"/>
     </row>
-    <row r="2940" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2940" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2940" s="1"/>
     </row>
-    <row r="2941" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2941" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2941" s="1"/>
     </row>
-    <row r="2942" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2942" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2942" s="1"/>
     </row>
-    <row r="2943" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2943" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2943" s="1"/>
     </row>
-    <row r="2944" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2944" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2944" s="1"/>
-      <c r="D2944" s="1"/>
-    </row>
-    <row r="2945" spans="3:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2945" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2945" s="1"/>
     </row>
-    <row r="2946" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2946" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2946" s="1"/>
     </row>
-    <row r="2947" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2947" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2947" s="1"/>
     </row>
-    <row r="2948" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2948" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2948" s="1"/>
     </row>
-    <row r="2949" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2949" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2949" s="1"/>
-    </row>
-    <row r="2950" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D2949" s="1"/>
+    </row>
+    <row r="2950" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2950" s="1"/>
     </row>
-    <row r="2951" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2951" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2951" s="1"/>
     </row>
-    <row r="2952" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2952" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2952" s="1"/>
     </row>
-    <row r="2953" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2953" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2953" s="1"/>
     </row>
-    <row r="2954" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2954" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2954" s="1"/>
     </row>
-    <row r="2955" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2955" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2955" s="1"/>
     </row>
-    <row r="2956" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2956" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2956" s="1"/>
     </row>
-    <row r="2957" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2957" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2957" s="1"/>
     </row>
-    <row r="2958" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2958" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2958" s="1"/>
     </row>
-    <row r="2959" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2959" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2959" s="1"/>
     </row>
-    <row r="2960" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2960" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2960" s="1"/>
     </row>
     <row r="2961" spans="3:3" x14ac:dyDescent="0.25">
@@ -4241,7 +4367,6 @@
     </row>
     <row r="2981" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2981" s="1"/>
-      <c r="D2981" s="1"/>
     </row>
     <row r="2982" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2982" s="1"/>
@@ -4257,6 +4382,7 @@
     </row>
     <row r="2986" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2986" s="1"/>
+      <c r="D2986" s="1"/>
     </row>
     <row r="2987" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2987" s="1"/>
@@ -4479,7 +4605,6 @@
     </row>
     <row r="3060" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3060" s="1"/>
-      <c r="D3060" s="1"/>
     </row>
     <row r="3061" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3061" s="1"/>
@@ -4495,6 +4620,7 @@
     </row>
     <row r="3065" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3065" s="1"/>
+      <c r="D3065" s="1"/>
     </row>
     <row r="3066" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3066" s="1"/>
@@ -4576,7 +4702,6 @@
     </row>
     <row r="3092" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3092" s="1"/>
-      <c r="D3092" s="1"/>
     </row>
     <row r="3093" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3093" s="1"/>
@@ -4592,6 +4717,7 @@
     </row>
     <row r="3097" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3097" s="1"/>
+      <c r="D3097" s="1"/>
     </row>
     <row r="3098" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3098" s="1"/>
@@ -4676,7 +4802,6 @@
     </row>
     <row r="3125" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3125" s="1"/>
-      <c r="D3125" s="1"/>
     </row>
     <row r="3126" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3126" s="1"/>
@@ -4692,6 +4817,7 @@
     </row>
     <row r="3130" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3130" s="1"/>
+      <c r="D3130" s="1"/>
     </row>
     <row r="3131" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3131" s="1"/>
@@ -4999,101 +5125,101 @@
     <row r="3232" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3232" s="1"/>
     </row>
-    <row r="3233" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3233" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3233" s="1"/>
     </row>
-    <row r="3234" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3234" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3234" s="1"/>
     </row>
-    <row r="3235" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3235" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3235" s="1"/>
     </row>
-    <row r="3236" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3236" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3236" s="1"/>
     </row>
-    <row r="3237" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3237" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3237" s="1"/>
     </row>
-    <row r="3238" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3238" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3238" s="1"/>
     </row>
-    <row r="3239" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3239" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3239" s="1"/>
     </row>
-    <row r="3240" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3240" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3240" s="1"/>
     </row>
-    <row r="3241" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3241" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3241" s="1"/>
     </row>
-    <row r="3242" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3242" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3242" s="1"/>
     </row>
-    <row r="3243" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3243" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3243" s="1"/>
     </row>
-    <row r="3244" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3244" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3244" s="1"/>
     </row>
-    <row r="3245" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3245" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3245" s="1"/>
     </row>
-    <row r="3246" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3246" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3246" s="1"/>
-      <c r="D3246" s="1"/>
-    </row>
-    <row r="3247" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3247" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3247" s="1"/>
     </row>
-    <row r="3248" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3248" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3248" s="1"/>
     </row>
-    <row r="3249" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3249" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3249" s="1"/>
     </row>
-    <row r="3250" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3250" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3250" s="1"/>
     </row>
-    <row r="3251" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3251" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3251" s="1"/>
-    </row>
-    <row r="3252" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3251" s="1"/>
+    </row>
+    <row r="3252" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3252" s="1"/>
     </row>
-    <row r="3253" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3253" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3253" s="1"/>
     </row>
-    <row r="3254" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3254" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3254" s="1"/>
     </row>
-    <row r="3255" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3255" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3255" s="1"/>
     </row>
-    <row r="3256" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3256" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3256" s="1"/>
     </row>
-    <row r="3257" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3257" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3257" s="1"/>
     </row>
-    <row r="3258" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3258" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3258" s="1"/>
     </row>
-    <row r="3259" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3259" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3259" s="1"/>
     </row>
-    <row r="3260" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3260" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3260" s="1"/>
     </row>
-    <row r="3261" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3261" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3261" s="1"/>
     </row>
-    <row r="3262" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3262" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3262" s="1"/>
     </row>
-    <row r="3263" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3263" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3263" s="1"/>
     </row>
-    <row r="3264" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3264" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3264" s="1"/>
     </row>
     <row r="3265" spans="3:4" x14ac:dyDescent="0.25">
@@ -5119,14 +5245,12 @@
     </row>
     <row r="3272" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3272" s="1"/>
-      <c r="D3272" s="1"/>
     </row>
     <row r="3273" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3273" s="1"/>
     </row>
     <row r="3274" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3274" s="1"/>
-      <c r="D3274" s="1"/>
     </row>
     <row r="3275" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3275" s="1"/>
@@ -5136,63 +5260,65 @@
     </row>
     <row r="3277" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3277" s="1"/>
+      <c r="D3277" s="1"/>
     </row>
     <row r="3278" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3278" s="1"/>
     </row>
     <row r="3279" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3279" s="1"/>
+      <c r="D3279" s="1"/>
     </row>
     <row r="3280" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3280" s="1"/>
-      <c r="D3280" s="1"/>
-    </row>
-    <row r="3281" spans="3:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3281" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3281" s="1"/>
     </row>
-    <row r="3282" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3282" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3282" s="1"/>
     </row>
-    <row r="3283" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3283" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3283" s="1"/>
     </row>
-    <row r="3284" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3284" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3284" s="1"/>
     </row>
-    <row r="3285" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3285" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3285" s="1"/>
-    </row>
-    <row r="3286" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3285" s="1"/>
+    </row>
+    <row r="3286" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3286" s="1"/>
     </row>
-    <row r="3287" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3287" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3287" s="1"/>
     </row>
-    <row r="3288" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3288" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3288" s="1"/>
     </row>
-    <row r="3289" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3289" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3289" s="1"/>
     </row>
-    <row r="3290" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3290" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3290" s="1"/>
     </row>
-    <row r="3291" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3291" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3291" s="1"/>
     </row>
-    <row r="3292" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3292" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3292" s="1"/>
     </row>
-    <row r="3293" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3293" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3293" s="1"/>
     </row>
-    <row r="3294" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3294" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3294" s="1"/>
     </row>
-    <row r="3295" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3295" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3295" s="1"/>
     </row>
-    <row r="3296" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3296" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3296" s="1"/>
     </row>
     <row r="3297" spans="3:3" x14ac:dyDescent="0.25">
@@ -5305,7 +5431,6 @@
     </row>
     <row r="3333" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3333" s="1"/>
-      <c r="D3333" s="1"/>
     </row>
     <row r="3334" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3334" s="1"/>
@@ -5321,6 +5446,7 @@
     </row>
     <row r="3338" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3338" s="1"/>
+      <c r="D3338" s="1"/>
     </row>
     <row r="3339" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3339" s="1"/>
@@ -5580,101 +5706,101 @@
     <row r="3424" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3424" s="1"/>
     </row>
-    <row r="3425" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3425" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3425" s="1"/>
     </row>
-    <row r="3426" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3426" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3426" s="1"/>
     </row>
-    <row r="3427" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3427" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3427" s="1"/>
     </row>
-    <row r="3428" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3428" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3428" s="1"/>
     </row>
-    <row r="3429" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3429" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3429" s="1"/>
     </row>
-    <row r="3430" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3430" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3430" s="1"/>
     </row>
-    <row r="3431" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3431" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3431" s="1"/>
     </row>
-    <row r="3432" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3432" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3432" s="1"/>
     </row>
-    <row r="3433" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3433" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3433" s="1"/>
     </row>
-    <row r="3434" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3434" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3434" s="1"/>
     </row>
-    <row r="3435" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3435" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3435" s="1"/>
     </row>
-    <row r="3436" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3436" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3436" s="1"/>
     </row>
-    <row r="3437" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3437" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3437" s="1"/>
-      <c r="D3437" s="1"/>
-    </row>
-    <row r="3438" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3438" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3438" s="1"/>
     </row>
-    <row r="3439" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3439" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3439" s="1"/>
     </row>
-    <row r="3440" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3440" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3440" s="1"/>
     </row>
-    <row r="3441" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3441" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3441" s="1"/>
     </row>
-    <row r="3442" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3442" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3442" s="1"/>
-    </row>
-    <row r="3443" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D3442" s="1"/>
+    </row>
+    <row r="3443" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3443" s="1"/>
     </row>
-    <row r="3444" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3444" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3444" s="1"/>
     </row>
-    <row r="3445" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3445" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3445" s="1"/>
     </row>
-    <row r="3446" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3446" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3446" s="1"/>
     </row>
-    <row r="3447" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3447" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3447" s="1"/>
     </row>
-    <row r="3448" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3448" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3448" s="1"/>
     </row>
-    <row r="3449" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3449" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3449" s="1"/>
     </row>
-    <row r="3450" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3450" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3450" s="1"/>
     </row>
-    <row r="3451" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3451" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3451" s="1"/>
     </row>
-    <row r="3452" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3452" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3452" s="1"/>
     </row>
-    <row r="3453" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3453" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3453" s="1"/>
     </row>
-    <row r="3454" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3454" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3454" s="1"/>
     </row>
-    <row r="3455" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3455" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3455" s="1"/>
     </row>
-    <row r="3456" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3456" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3456" s="1"/>
     </row>
     <row r="3457" spans="3:3" x14ac:dyDescent="0.25">
@@ -5739,7 +5865,6 @@
     </row>
     <row r="3477" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3477" s="1"/>
-      <c r="D3477" s="1"/>
     </row>
     <row r="3478" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3478" s="1"/>
@@ -5755,6 +5880,7 @@
     </row>
     <row r="3482" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3482" s="1"/>
+      <c r="D3482" s="1"/>
     </row>
     <row r="3483" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3483" s="1"/>
@@ -5836,7 +5962,6 @@
     </row>
     <row r="3509" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3509" s="1"/>
-      <c r="D3509" s="1"/>
     </row>
     <row r="3510" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3510" s="1"/>
@@ -5852,6 +5977,7 @@
     </row>
     <row r="3514" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3514" s="1"/>
+      <c r="D3514" s="1"/>
     </row>
     <row r="3515" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3515" s="1"/>
@@ -6137,7 +6263,6 @@
     </row>
     <row r="3609" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3609" s="1"/>
-      <c r="D3609" s="1"/>
     </row>
     <row r="3610" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3610" s="1"/>
@@ -6153,6 +6278,7 @@
     </row>
     <row r="3614" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3614" s="1"/>
+      <c r="D3614" s="1"/>
     </row>
     <row r="3615" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3615" s="1"/>
@@ -6234,7 +6360,6 @@
     </row>
     <row r="3641" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3641" s="1"/>
-      <c r="D3641" s="1"/>
     </row>
     <row r="3642" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3642" s="1"/>
@@ -6250,6 +6375,7 @@
     </row>
     <row r="3646" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3646" s="1"/>
+      <c r="D3646" s="1"/>
     </row>
     <row r="3647" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3647" s="1"/>
@@ -6262,14 +6388,12 @@
     </row>
     <row r="3650" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3650" s="1"/>
-      <c r="D3650" s="1"/>
     </row>
     <row r="3651" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3651" s="1"/>
     </row>
     <row r="3652" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3652" s="1"/>
-      <c r="D3652" s="1"/>
     </row>
     <row r="3653" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3653" s="1"/>
@@ -6279,12 +6403,14 @@
     </row>
     <row r="3655" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3655" s="1"/>
+      <c r="D3655" s="1"/>
     </row>
     <row r="3656" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3656" s="1"/>
     </row>
     <row r="3657" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3657" s="1"/>
+      <c r="D3657" s="1"/>
     </row>
     <row r="3658" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3658" s="1"/>
@@ -6309,7 +6435,6 @@
     </row>
     <row r="3665" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3665" s="1"/>
-      <c r="D3665" s="1"/>
     </row>
     <row r="3666" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3666" s="1"/>
@@ -6319,36 +6444,36 @@
     </row>
     <row r="3668" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3668" s="1"/>
-      <c r="D3668" s="1"/>
     </row>
     <row r="3669" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3669" s="1"/>
     </row>
     <row r="3670" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3670" s="1"/>
+      <c r="D3670" s="1"/>
     </row>
     <row r="3671" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3671" s="1"/>
     </row>
     <row r="3672" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3672" s="1"/>
-      <c r="D3672" s="1"/>
     </row>
     <row r="3673" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3673" s="1"/>
+      <c r="D3673" s="1"/>
     </row>
     <row r="3674" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3674" s="1"/>
     </row>
     <row r="3675" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3675" s="1"/>
-      <c r="D3675" s="1"/>
     </row>
     <row r="3676" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3676" s="1"/>
     </row>
     <row r="3677" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3677" s="1"/>
+      <c r="D3677" s="1"/>
     </row>
     <row r="3678" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3678" s="1"/>
@@ -6358,10 +6483,10 @@
     </row>
     <row r="3680" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3680" s="1"/>
+      <c r="D3680" s="1"/>
     </row>
     <row r="3681" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3681" s="1"/>
-      <c r="D3681" s="1"/>
     </row>
     <row r="3682" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3682" s="1"/>
@@ -6371,13 +6496,13 @@
     </row>
     <row r="3684" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3684" s="1"/>
-      <c r="D3684" s="1"/>
     </row>
     <row r="3685" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3685" s="1"/>
     </row>
     <row r="3686" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3686" s="1"/>
+      <c r="D3686" s="1"/>
     </row>
     <row r="3687" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3687" s="1"/>
@@ -6388,6 +6513,22 @@
     <row r="3689" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3689" s="1"/>
       <c r="D3689" s="1"/>
+    </row>
+    <row r="3690" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3690" s="1"/>
+    </row>
+    <row r="3691" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3691" s="1"/>
+    </row>
+    <row r="3692" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3692" s="1"/>
+    </row>
+    <row r="3693" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3693" s="1"/>
+    </row>
+    <row r="3694" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3694" s="1"/>
+      <c r="D3694" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/SeguimientoCeldas.xlsx
+++ b/data/SeguimientoCeldas.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\project\ubuntu\dashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Documents\project\ubuntu\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB6EAD4-9D84-4864-A3D7-DCFC99D77110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4026D7-229B-4E02-939E-8B8916A3B6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EAA44A74-7458-4EF0-BC24-1E591EA6BFE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Seguimiento" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seguimiento!$A$1:$C$59</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
   <si>
     <t>CellName</t>
   </si>
@@ -199,9 +199,6 @@
     <t>NODO3_GUAJALO_SAN_MARTIN1_CARR4</t>
   </si>
   <si>
-    <t>REAL_AUDIENCIA1</t>
-  </si>
-  <si>
     <t>PIC_SMALL_ANT1</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>Pendiente Cambio RRU</t>
   </si>
   <si>
-    <t>Pendiente Trabajos Infraestructura</t>
-  </si>
-  <si>
     <t>COL_EINSTEIN1</t>
   </si>
   <si>
@@ -250,12 +244,6 @@
     <t>44221-3</t>
   </si>
   <si>
-    <t>ORE_JOY_JOYA_DE_LOS_SACHAS_L21_3</t>
-  </si>
-  <si>
-    <t>44863-3</t>
-  </si>
-  <si>
     <t>Daño en RRU</t>
   </si>
   <si>
@@ -269,6 +257,21 @@
   </si>
   <si>
     <t>Celda Bloqueada</t>
+  </si>
+  <si>
+    <t>PUERTO_BAQUERIZO1</t>
+  </si>
+  <si>
+    <t>NAIQ3</t>
+  </si>
+  <si>
+    <t>Daño en Sistema Radiante</t>
+  </si>
+  <si>
+    <t>SMALL_UIO_ITCHIMBIA11</t>
+  </si>
+  <si>
+    <t>Equipo Desmontado</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BDB550-E1E7-404D-B978-F462E546FC21}">
-  <dimension ref="A1:D3694"/>
+  <dimension ref="A1:D3692"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
@@ -1559,7 +1562,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41">
         <v>42211</v>
@@ -1570,7 +1573,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42">
         <v>42212</v>
@@ -1581,7 +1584,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B43">
         <v>42213</v>
@@ -1592,10 +1595,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
         <v>72</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
       </c>
       <c r="C44" t="s">
         <v>37</v>
@@ -1603,10 +1606,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
         <v>71</v>
-      </c>
-      <c r="B45" t="s">
-        <v>73</v>
       </c>
       <c r="C45" t="s">
         <v>37</v>
@@ -1625,7 +1628,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>32801</v>
@@ -1636,7 +1639,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B48">
         <v>42481</v>
@@ -1647,7 +1650,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49">
         <v>42482</v>
@@ -1658,7 +1661,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50">
         <v>42483</v>
@@ -1669,43 +1672,43 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51">
-        <v>41481</v>
+        <v>62</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" t="s">
         <v>64</v>
       </c>
+      <c r="B52">
+        <v>32061</v>
+      </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B53">
-        <v>32061</v>
+        <v>49574</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54">
-        <v>49574</v>
+        <v>49575</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -1713,21 +1716,21 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B55">
-        <v>49575</v>
+        <v>46031</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C56" t="s">
         <v>26</v>
@@ -1735,10 +1738,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C57" t="s">
         <v>26</v>
@@ -1746,10 +1749,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B58">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="C58" t="s">
         <v>26</v>
@@ -1757,10 +1760,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C59" t="s">
         <v>26</v>
@@ -1768,21 +1771,21 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B60">
-        <v>46039</v>
+        <v>48741</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>75</v>
       </c>
-      <c r="B61" t="s">
-        <v>76</v>
+      <c r="B61">
+        <v>48742</v>
       </c>
       <c r="C61" t="s">
         <v>77</v>
@@ -1790,57 +1793,85 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B62">
-        <v>48741</v>
+        <v>48743</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63">
-        <v>48742</v>
+        <v>49211</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64">
+        <v>49217</v>
+      </c>
+      <c r="C64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65">
+        <v>42893</v>
+      </c>
+      <c r="C65" t="s">
         <v>80</v>
       </c>
-      <c r="B64">
-        <v>48743</v>
-      </c>
-      <c r="C64" t="s">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="1007" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1007" s="1"/>
-    </row>
-    <row r="1146" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1146" s="1"/>
-    </row>
-    <row r="1338" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1338" s="1"/>
-    </row>
-    <row r="1522" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1522" s="1"/>
-    </row>
-    <row r="1576" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1576" s="1"/>
-    </row>
-    <row r="1654" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D1654" s="1"/>
-    </row>
-    <row r="2060" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2060" s="1"/>
+      <c r="B66">
+        <v>32721</v>
+      </c>
+      <c r="C66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1005" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1005" s="1"/>
+    </row>
+    <row r="1144" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1144" s="1"/>
+    </row>
+    <row r="1336" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1336" s="1"/>
+    </row>
+    <row r="1520" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1520" s="1"/>
+    </row>
+    <row r="1574" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1574" s="1"/>
+    </row>
+    <row r="1652" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1652" s="1"/>
+    </row>
+    <row r="2058" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D2058" s="1"/>
+    </row>
+    <row r="2140" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2140" s="1"/>
+    </row>
+    <row r="2141" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2141" s="1"/>
     </row>
     <row r="2142" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2142" s="1"/>
@@ -2003,13 +2034,13 @@
     </row>
     <row r="2195" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2195" s="1"/>
+      <c r="D2195" s="1"/>
     </row>
     <row r="2196" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2196" s="1"/>
     </row>
     <row r="2197" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2197" s="1"/>
-      <c r="D2197" s="1"/>
     </row>
     <row r="2198" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2198" s="1"/>
@@ -2098,12 +2129,12 @@
     <row r="2226" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2226" s="1"/>
     </row>
-    <row r="2227" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2227" s="1"/>
-    </row>
     <row r="2228" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2228" s="1"/>
     </row>
+    <row r="2229" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2229" s="1"/>
+    </row>
     <row r="2230" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2230" s="1"/>
     </row>
@@ -2508,13 +2539,13 @@
     </row>
     <row r="2364" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2364" s="1"/>
+      <c r="D2364" s="1"/>
     </row>
     <row r="2365" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2365" s="1"/>
     </row>
     <row r="2366" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2366" s="1"/>
-      <c r="D2366" s="1"/>
     </row>
     <row r="2367" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2367" s="1"/>
@@ -2578,13 +2609,13 @@
     </row>
     <row r="2387" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2387" s="1"/>
+      <c r="D2387" s="1"/>
     </row>
     <row r="2388" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2388" s="1"/>
     </row>
     <row r="2389" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2389" s="1"/>
-      <c r="D2389" s="1"/>
     </row>
     <row r="2390" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2390" s="1"/>
@@ -3188,13 +3219,13 @@
     </row>
     <row r="2590" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2590" s="1"/>
+      <c r="D2590" s="1"/>
     </row>
     <row r="2591" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2591" s="1"/>
     </row>
     <row r="2592" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2592" s="1"/>
-      <c r="D2592" s="1"/>
     </row>
     <row r="2593" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2593" s="1"/>
@@ -3282,13 +3313,13 @@
     </row>
     <row r="2621" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2621" s="1"/>
+      <c r="D2621" s="1"/>
     </row>
     <row r="2622" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2622" s="1"/>
     </row>
     <row r="2623" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2623" s="1"/>
-      <c r="D2623" s="1"/>
     </row>
     <row r="2624" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2624" s="1"/>
@@ -3718,13 +3749,13 @@
     </row>
     <row r="2766" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2766" s="1"/>
+      <c r="D2766" s="1"/>
     </row>
     <row r="2767" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2767" s="1"/>
     </row>
     <row r="2768" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2768" s="1"/>
-      <c r="D2768" s="1"/>
     </row>
     <row r="2769" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2769" s="1"/>
@@ -3959,13 +3990,13 @@
     </row>
     <row r="2846" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2846" s="1"/>
+      <c r="D2846" s="1"/>
     </row>
     <row r="2847" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2847" s="1"/>
     </row>
     <row r="2848" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2848" s="1"/>
-      <c r="D2848" s="1"/>
     </row>
     <row r="2849" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2849" s="1"/>
@@ -4065,13 +4096,13 @@
     </row>
     <row r="2881" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2881" s="1"/>
+      <c r="D2881" s="1"/>
     </row>
     <row r="2882" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2882" s="1"/>
     </row>
     <row r="2883" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2883" s="1"/>
-      <c r="D2883" s="1"/>
     </row>
     <row r="2884" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2884" s="1"/>
@@ -4264,13 +4295,13 @@
     </row>
     <row r="2947" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2947" s="1"/>
+      <c r="D2947" s="1"/>
     </row>
     <row r="2948" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2948" s="1"/>
     </row>
     <row r="2949" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2949" s="1"/>
-      <c r="D2949" s="1"/>
     </row>
     <row r="2950" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2950" s="1"/>
@@ -4376,13 +4407,13 @@
     </row>
     <row r="2984" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2984" s="1"/>
+      <c r="D2984" s="1"/>
     </row>
     <row r="2985" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2985" s="1"/>
     </row>
     <row r="2986" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2986" s="1"/>
-      <c r="D2986" s="1"/>
     </row>
     <row r="2987" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2987" s="1"/>
@@ -4614,13 +4645,13 @@
     </row>
     <row r="3063" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3063" s="1"/>
+      <c r="D3063" s="1"/>
     </row>
     <row r="3064" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3064" s="1"/>
     </row>
     <row r="3065" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3065" s="1"/>
-      <c r="D3065" s="1"/>
     </row>
     <row r="3066" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3066" s="1"/>
@@ -4711,13 +4742,13 @@
     </row>
     <row r="3095" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3095" s="1"/>
+      <c r="D3095" s="1"/>
     </row>
     <row r="3096" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3096" s="1"/>
     </row>
     <row r="3097" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3097" s="1"/>
-      <c r="D3097" s="1"/>
     </row>
     <row r="3098" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3098" s="1"/>
@@ -4811,13 +4842,13 @@
     </row>
     <row r="3128" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3128" s="1"/>
+      <c r="D3128" s="1"/>
     </row>
     <row r="3129" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3129" s="1"/>
     </row>
     <row r="3130" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3130" s="1"/>
-      <c r="D3130" s="1"/>
     </row>
     <row r="3131" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3131" s="1"/>
@@ -5175,13 +5206,13 @@
     </row>
     <row r="3249" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3249" s="1"/>
+      <c r="D3249" s="1"/>
     </row>
     <row r="3250" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3250" s="1"/>
     </row>
     <row r="3251" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3251" s="1"/>
-      <c r="D3251" s="1"/>
     </row>
     <row r="3252" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3252" s="1"/>
@@ -5254,6 +5285,7 @@
     </row>
     <row r="3275" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3275" s="1"/>
+      <c r="D3275" s="1"/>
     </row>
     <row r="3276" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3276" s="1"/>
@@ -5267,7 +5299,6 @@
     </row>
     <row r="3279" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3279" s="1"/>
-      <c r="D3279" s="1"/>
     </row>
     <row r="3280" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3280" s="1"/>
@@ -5280,13 +5311,13 @@
     </row>
     <row r="3283" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3283" s="1"/>
+      <c r="D3283" s="1"/>
     </row>
     <row r="3284" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3284" s="1"/>
     </row>
     <row r="3285" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3285" s="1"/>
-      <c r="D3285" s="1"/>
     </row>
     <row r="3286" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3286" s="1"/>
@@ -5440,13 +5471,13 @@
     </row>
     <row r="3336" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3336" s="1"/>
+      <c r="D3336" s="1"/>
     </row>
     <row r="3337" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3337" s="1"/>
     </row>
     <row r="3338" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3338" s="1"/>
-      <c r="D3338" s="1"/>
     </row>
     <row r="3339" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3339" s="1"/>
@@ -5706,101 +5737,101 @@
     <row r="3424" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3424" s="1"/>
     </row>
-    <row r="3425" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3425" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3425" s="1"/>
     </row>
-    <row r="3426" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3426" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3426" s="1"/>
     </row>
-    <row r="3427" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3427" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3427" s="1"/>
     </row>
-    <row r="3428" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3428" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3428" s="1"/>
     </row>
-    <row r="3429" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3429" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3429" s="1"/>
     </row>
-    <row r="3430" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3430" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3430" s="1"/>
     </row>
-    <row r="3431" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3431" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3431" s="1"/>
     </row>
-    <row r="3432" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3432" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3432" s="1"/>
     </row>
-    <row r="3433" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3433" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3433" s="1"/>
     </row>
-    <row r="3434" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3434" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3434" s="1"/>
     </row>
-    <row r="3435" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3435" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3435" s="1"/>
     </row>
-    <row r="3436" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3436" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3436" s="1"/>
     </row>
-    <row r="3437" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3437" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3437" s="1"/>
     </row>
-    <row r="3438" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3438" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3438" s="1"/>
     </row>
-    <row r="3439" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3439" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3439" s="1"/>
     </row>
-    <row r="3440" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3440" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3440" s="1"/>
-    </row>
-    <row r="3441" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D3440" s="1"/>
+    </row>
+    <row r="3441" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3441" s="1"/>
     </row>
-    <row r="3442" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3442" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3442" s="1"/>
-      <c r="D3442" s="1"/>
-    </row>
-    <row r="3443" spans="3:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3443" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3443" s="1"/>
     </row>
-    <row r="3444" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3444" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3444" s="1"/>
     </row>
-    <row r="3445" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3445" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3445" s="1"/>
     </row>
-    <row r="3446" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3446" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3446" s="1"/>
     </row>
-    <row r="3447" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3447" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3447" s="1"/>
     </row>
-    <row r="3448" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3448" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3448" s="1"/>
     </row>
-    <row r="3449" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3449" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3449" s="1"/>
     </row>
-    <row r="3450" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3450" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3450" s="1"/>
     </row>
-    <row r="3451" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3451" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3451" s="1"/>
     </row>
-    <row r="3452" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3452" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3452" s="1"/>
     </row>
-    <row r="3453" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3453" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3453" s="1"/>
     </row>
-    <row r="3454" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3454" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3454" s="1"/>
     </row>
-    <row r="3455" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3455" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3455" s="1"/>
     </row>
-    <row r="3456" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3456" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3456" s="1"/>
     </row>
     <row r="3457" spans="3:3" x14ac:dyDescent="0.25">
@@ -5874,13 +5905,13 @@
     </row>
     <row r="3480" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3480" s="1"/>
+      <c r="D3480" s="1"/>
     </row>
     <row r="3481" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3481" s="1"/>
     </row>
     <row r="3482" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3482" s="1"/>
-      <c r="D3482" s="1"/>
     </row>
     <row r="3483" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3483" s="1"/>
@@ -5971,13 +6002,13 @@
     </row>
     <row r="3512" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3512" s="1"/>
+      <c r="D3512" s="1"/>
     </row>
     <row r="3513" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3513" s="1"/>
     </row>
     <row r="3514" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3514" s="1"/>
-      <c r="D3514" s="1"/>
     </row>
     <row r="3515" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3515" s="1"/>
@@ -6272,13 +6303,13 @@
     </row>
     <row r="3612" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3612" s="1"/>
+      <c r="D3612" s="1"/>
     </row>
     <row r="3613" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3613" s="1"/>
     </row>
     <row r="3614" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3614" s="1"/>
-      <c r="D3614" s="1"/>
     </row>
     <row r="3615" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3615" s="1"/>
@@ -6369,13 +6400,13 @@
     </row>
     <row r="3644" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3644" s="1"/>
+      <c r="D3644" s="1"/>
     </row>
     <row r="3645" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3645" s="1"/>
     </row>
     <row r="3646" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3646" s="1"/>
-      <c r="D3646" s="1"/>
     </row>
     <row r="3647" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3647" s="1"/>
@@ -6397,6 +6428,7 @@
     </row>
     <row r="3653" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3653" s="1"/>
+      <c r="D3653" s="1"/>
     </row>
     <row r="3654" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3654" s="1"/>
@@ -6410,7 +6442,6 @@
     </row>
     <row r="3657" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3657" s="1"/>
-      <c r="D3657" s="1"/>
     </row>
     <row r="3658" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3658" s="1"/>
@@ -6444,46 +6475,46 @@
     </row>
     <row r="3668" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3668" s="1"/>
+      <c r="D3668" s="1"/>
     </row>
     <row r="3669" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3669" s="1"/>
     </row>
     <row r="3670" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3670" s="1"/>
-      <c r="D3670" s="1"/>
     </row>
     <row r="3671" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3671" s="1"/>
+      <c r="D3671" s="1"/>
     </row>
     <row r="3672" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3672" s="1"/>
     </row>
     <row r="3673" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3673" s="1"/>
-      <c r="D3673" s="1"/>
     </row>
     <row r="3674" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3674" s="1"/>
     </row>
     <row r="3675" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3675" s="1"/>
+      <c r="D3675" s="1"/>
     </row>
     <row r="3676" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3676" s="1"/>
     </row>
     <row r="3677" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3677" s="1"/>
-      <c r="D3677" s="1"/>
     </row>
     <row r="3678" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3678" s="1"/>
+      <c r="D3678" s="1"/>
     </row>
     <row r="3679" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3679" s="1"/>
     </row>
     <row r="3680" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3680" s="1"/>
-      <c r="D3680" s="1"/>
     </row>
     <row r="3681" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3681" s="1"/>
@@ -6496,23 +6527,23 @@
     </row>
     <row r="3684" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3684" s="1"/>
+      <c r="D3684" s="1"/>
     </row>
     <row r="3685" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3685" s="1"/>
     </row>
     <row r="3686" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3686" s="1"/>
-      <c r="D3686" s="1"/>
     </row>
     <row r="3687" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3687" s="1"/>
+      <c r="D3687" s="1"/>
     </row>
     <row r="3688" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3688" s="1"/>
     </row>
     <row r="3689" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3689" s="1"/>
-      <c r="D3689" s="1"/>
     </row>
     <row r="3690" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3690" s="1"/>
@@ -6522,13 +6553,7 @@
     </row>
     <row r="3692" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3692" s="1"/>
-    </row>
-    <row r="3693" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3693" s="1"/>
-    </row>
-    <row r="3694" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C3694" s="1"/>
-      <c r="D3694" s="1"/>
+      <c r="D3692" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
